--- a/results/results.xlsx
+++ b/results/results.xlsx
@@ -10,13 +10,15 @@
     <sheet name="汇总" sheetId="1" r:id="rId1"/>
     <sheet name="校验" sheetId="2" r:id="rId2"/>
     <sheet name="概率" sheetId="3" r:id="rId3"/>
+    <sheet name="敏感性" sheetId="4" r:id="rId4"/>
+    <sheet name="参数来源" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="545" uniqueCount="86">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1056" uniqueCount="342">
   <si>
     <t>模型</t>
   </si>
@@ -274,6 +276,774 @@
   </si>
   <si>
     <t>冬季</t>
+  </si>
+  <si>
+    <t>参数</t>
+  </si>
+  <si>
+    <t>取值</t>
+  </si>
+  <si>
+    <t>kappa</t>
+  </si>
+  <si>
+    <t>FLOAT</t>
+  </si>
+  <si>
+    <t>R_TH</t>
+  </si>
+  <si>
+    <t>BETA_LIQ</t>
+  </si>
+  <si>
+    <t>C_W</t>
+  </si>
+  <si>
+    <t>参数(符号)</t>
+  </si>
+  <si>
+    <t>合理范围/对比</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>数据年份</t>
+  </si>
+  <si>
+    <t>来源</t>
+  </si>
+  <si>
+    <t>可信度</t>
+  </si>
+  <si>
+    <t>使用位置</t>
+  </si>
+  <si>
+    <t>时间序列</t>
+  </si>
+  <si>
+    <t>电价</t>
+  </si>
+  <si>
+    <t>GPU</t>
+  </si>
+  <si>
+    <t>热</t>
+  </si>
+  <si>
+    <t>冷却</t>
+  </si>
+  <si>
+    <t>储能</t>
+  </si>
+  <si>
+    <t>经济</t>
+  </si>
+  <si>
+    <t>任务</t>
+  </si>
+  <si>
+    <t>规划</t>
+  </si>
+  <si>
+    <t>DRO</t>
+  </si>
+  <si>
+    <t>实时任务到达 A^R_dst</t>
+  </si>
+  <si>
+    <t>可延期任务到达 A^B_dst</t>
+  </si>
+  <si>
+    <t>环境干球温度 T_amb</t>
+  </si>
+  <si>
+    <t>光伏单位出力 g^PV</t>
+  </si>
+  <si>
+    <t>交易电价平段 λ_E</t>
+  </si>
+  <si>
+    <t>输配电价(1–10 kV 两部制电量电价) c_TD</t>
+  </si>
+  <si>
+    <t>峰谷浮动比例</t>
+  </si>
+  <si>
+    <t>时段划分</t>
+  </si>
+  <si>
+    <t>GPU 热设计功率 TDP</t>
+  </si>
+  <si>
+    <t>主机功率分摊 P_host</t>
+  </si>
+  <si>
+    <t>GPU 空闲功率</t>
+  </si>
+  <si>
+    <t>模式 k2 浅锁频 (v p)</t>
+  </si>
+  <si>
+    <t>模式 k3 深锁频 (v p)</t>
+  </si>
+  <si>
+    <t>实时任务可用模式集 K_R</t>
+  </si>
+  <si>
+    <t>允许热点温度 T^chip_max</t>
+  </si>
+  <si>
+    <t>等效热阻 R^th</t>
+  </si>
+  <si>
+    <t>液冷温区 [T_j下 T_j上]</t>
+  </si>
+  <si>
+    <t>液冷捕获比例 β_liq</t>
+  </si>
+  <si>
+    <t>干冷器设计进口温差 ITD_des</t>
+  </si>
+  <si>
+    <t>干冷器风机电耗 a^FC</t>
+  </si>
+  <si>
+    <t>冷水机组 COP (AHRI 工况)</t>
+  </si>
+  <si>
+    <t>高水温 COP 上限 COP_max</t>
+  </si>
+  <si>
+    <t>主循环泵电耗 a^circ</t>
+  </si>
+  <si>
+    <t>空气侧单位散热电耗 a^air</t>
+  </si>
+  <si>
+    <t>IT 侧配电损耗 δ_e</t>
+  </si>
+  <si>
+    <t>液冷环路等效热容 C_w</t>
+  </si>
+  <si>
+    <t>CDU 换热端差 ΔT_CDU</t>
+  </si>
+  <si>
+    <t>往返效率</t>
+  </si>
+  <si>
+    <t>SOC 边界与初末值</t>
+  </si>
+  <si>
+    <t>最大倍率 c_B^max</t>
+  </si>
+  <si>
+    <t>GPU 单位投资(含整机分摊)</t>
+  </si>
+  <si>
+    <t>GPU 寿命与运维</t>
+  </si>
+  <si>
+    <t>光伏单位投资</t>
+  </si>
+  <si>
+    <t>光伏寿命与运维</t>
+  </si>
+  <si>
+    <t>储能能量单位投资</t>
+  </si>
+  <si>
+    <t>储能功率(PCS)单位投资</t>
+  </si>
+  <si>
+    <t>储能寿命</t>
+  </si>
+  <si>
+    <t>干冷器单位投资</t>
+  </si>
+  <si>
+    <t>冷水机组单位投资</t>
+  </si>
+  <si>
+    <t>冷源寿命</t>
+  </si>
+  <si>
+    <t>折现率</t>
+  </si>
+  <si>
+    <t>汇率</t>
+  </si>
+  <si>
+    <t>可延期任务最大延期 D</t>
+  </si>
+  <si>
+    <t>容量上限 x̄</t>
+  </si>
+  <si>
+    <t>电网接入容量</t>
+  </si>
+  <si>
+    <t>模糊集 δ_d v±</t>
+  </si>
+  <si>
+    <t>BurstGPT 对话日志逐时 token 量(第9–60天; 6:00 起算) 规模化至年均 500</t>
+  </si>
+  <si>
+    <t>BurstGPT API 日志逐时 token 量 规模化至年均 200</t>
+  </si>
+  <si>
+    <t>NREL TMY3 Denver Intl 725650 (BSk 半干旱; 海拔1650 m) 作为宁夏中卫的替代气象</t>
+  </si>
+  <si>
+    <t>pvlib + PVWatts v5 由 TMY3 辐照计算; 倾角35° 正南; 容配比1.2</t>
+  </si>
+  <si>
+    <t>0.289</t>
+  </si>
+  <si>
+    <t>0.0920</t>
+  </si>
+  <si>
+    <t>±50%</t>
+  </si>
+  <si>
+    <t>高峰 7–9 17–23 时; 低谷 9–17 时; 其余平段</t>
+  </si>
+  <si>
+    <t>0.700</t>
+  </si>
+  <si>
+    <t>0.467</t>
+  </si>
+  <si>
+    <t>0.20×TDP = 0.140</t>
+  </si>
+  <si>
+    <t>v=0.95 p_gpu=0.87×TDP</t>
+  </si>
+  <si>
+    <t>v=0.93 p_gpu=0.80×TDP</t>
+  </si>
+  <si>
+    <t>{k1 k2}</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>57.1 (由 700 W 满功率在 45 ℃ 进水恰达 85 ℃ 反推)</t>
+  </si>
+  <si>
+    <t>[25 32] [32 38] [38 45] [45 50] [50 53]</t>
+  </si>
+  <si>
+    <t>0.75</t>
+  </si>
+  <si>
+    <t>11.1</t>
+  </si>
+  <si>
+    <t>0.045</t>
+  </si>
+  <si>
+    <t>2.96</t>
+  </si>
+  <si>
+    <t>8.0</t>
+  </si>
+  <si>
+    <t>0.0170</t>
+  </si>
+  <si>
+    <t>0.338</t>
+  </si>
+  <si>
+    <t>0.08</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0.85 (η_c=η_d=0.922)</t>
+  </si>
+  <si>
+    <t>0.10/0.90/0.50</t>
+  </si>
+  <si>
+    <t>0.5</t>
+  </si>
+  <si>
+    <t>46875 USD = 336956 元/台</t>
+  </si>
+  <si>
+    <t>5 年; 625 USD/台·年</t>
+  </si>
+  <si>
+    <t>3160</t>
+  </si>
+  <si>
+    <t>25 年; 1.5%/年</t>
+  </si>
+  <si>
+    <t>1034 (EPC 1089.02 元/kWh 扣除 PCS)</t>
+  </si>
+  <si>
+    <t>110</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>540 (264 USD/RT)</t>
+  </si>
+  <si>
+    <t>2453 (1200 USD/RT)</t>
+  </si>
+  <si>
+    <t>干冷器 20; 冷水机组 23</t>
+  </si>
+  <si>
+    <t>7.1884</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>N 4096; PV 8000; P_B 4000; E_B 16000; FC/MC 8000</t>
+  </si>
+  <si>
+    <t>10000</t>
+  </si>
+  <si>
+    <t>bootstrap 2000 次 95% 分位数</t>
+  </si>
+  <si>
+    <t>逐时均值峰谷比约 33 倍(凌晨近零); 可用 51 日</t>
+  </si>
+  <si>
+    <t>日最大总量为均值的 5.6 倍(极端突发)</t>
+  </si>
+  <si>
+    <t>年均 10.9 ℃; 最高 40.0 ℃</t>
+  </si>
+  <si>
+    <t>年利用 1526 h(中卫站数据待替换后重算)</t>
+  </si>
+  <si>
+    <t>2024 年 0.289; 2025 年 0.271</t>
+  </si>
+  <si>
+    <t>35 kV 0.0769; 110 kV 0.0600</t>
+  </si>
+  <si>
+    <t>征求意见稿: 新能源 ±30%; 尖峰/深谷 ±80%</t>
+  </si>
+  <si>
+    <t>与 2024-01 实测峰谷价差约 0.28 元/kWh 一致</t>
+  </si>
+  <si>
+    <t>—</t>
+  </si>
+  <si>
+    <t>DGX H100 最大 10.2 kW/8 = 1.275 kW/台 为上界</t>
+  </si>
+  <si>
+    <t>BLOOM: 5% 性能损失 ↔ 13% 峰值功率下降; 降频约 7% 时性能损失&lt;2%</t>
+  </si>
+  <si>
+    <t>up to 20% power for up to 7% performance loss; H100 token 阶段 700→350 W 几乎无时延影响(Splitwise)</t>
+  </si>
+  <si>
+    <t>POLCA 对高优先级仅轻度降频(A100 1305 MHz)</t>
+  </si>
+  <si>
+    <t>A100 Max Operating 85 ℃; H100 slowdown 约 87 ℃ shutdown 约 90 ℃</t>
+  </si>
+  <si>
+    <t>JetCool 冷板 21 K/kW(仅冷板); Lenovo 18 ℃ 进水裕度&gt;20 K</t>
+  </si>
+  <si>
+    <t>ASHRAE W17/W27/W32/W40/W45/W+</t>
+  </si>
+  <si>
+    <t>0.60–0.80 (冷板); 全液冷节点宣称约 100%</t>
+  </si>
+  <si>
+    <t>最小逼近 20 °F</t>
+  </si>
+  <si>
+    <t>厂家额定 0.01–0.034 (Extrcool/Supermicro)</t>
+  </si>
+  <si>
+    <t>风冷 ≥150 RT EER 10.1; 水冷离心 0.61 kW/RT ≈ COP 5.77</t>
+  </si>
+  <si>
+    <t>需厂家曲线</t>
+  </si>
+  <si>
+    <t>≤0.010 (Aeons 设计目标)</t>
+  </si>
+  <si>
+    <t>按 AHRI 工况 COP</t>
+  </si>
+  <si>
+    <t>8–12% (行业报道 未核对原文)</t>
+  </si>
+  <si>
+    <t>敏感性 10–90</t>
+  </si>
+  <si>
+    <t>2–5</t>
+  </si>
+  <si>
+    <t>0.85–0.90</t>
+  </si>
+  <si>
+    <t>2 h 系统</t>
+  </si>
+  <si>
+    <t>H100 约 3 万 USD/卡; 整机 375k USD/台(8卡); 云租 38 USD/h·DGX</t>
+  </si>
+  <si>
+    <t>4–6 年; 维护 5000 USD/服务器·年</t>
+  </si>
+  <si>
+    <t>2023 地面 3.40; 工商业分布式约 2.75; IRENA 2024 全球 691 USD/kW</t>
+  </si>
+  <si>
+    <t>1–2%/年</t>
+  </si>
+  <si>
+    <t>系统中标 0.574(2024-07)–0.697(2024-12) 元/Wh; 年初约 0.8</t>
+  </si>
+  <si>
+    <t>集中式 0.08 元/W; 组串式 0.11 元/W</t>
+  </si>
+  <si>
+    <t>整套工业冷却约 300 USD/kW (Thunder Said)</t>
+  </si>
+  <si>
+    <t>6–8%</t>
+  </si>
+  <si>
+    <t>2024-11 至 12 月 7.18–7.19</t>
+  </si>
+  <si>
+    <t>Batch API 24 h 完成窗口</t>
+  </si>
+  <si>
+    <t>κ∈{0 0.5 1 2 4}</t>
+  </si>
+  <si>
+    <t>GPU·h_nom/h</t>
+  </si>
+  <si>
+    <t>℃</t>
+  </si>
+  <si>
+    <t>kW_ac/kWp</t>
+  </si>
+  <si>
+    <t>元/kWh</t>
+  </si>
+  <si>
+    <t>kW</t>
+  </si>
+  <si>
+    <t>kW/台</t>
+  </si>
+  <si>
+    <t>—/kW</t>
+  </si>
+  <si>
+    <t>K/kW</t>
+  </si>
+  <si>
+    <t>K</t>
+  </si>
+  <si>
+    <t>kWe/kWth</t>
+  </si>
+  <si>
+    <t>kWh/K</t>
+  </si>
+  <si>
+    <t>1/h</t>
+  </si>
+  <si>
+    <t>元/台</t>
+  </si>
+  <si>
+    <t>年</t>
+  </si>
+  <si>
+    <t>元/kWp</t>
+  </si>
+  <si>
+    <t>元/kW</t>
+  </si>
+  <si>
+    <t>元/kWth</t>
+  </si>
+  <si>
+    <t>元/USD</t>
+  </si>
+  <si>
+    <t>h</t>
+  </si>
+  <si>
+    <t>多种</t>
+  </si>
+  <si>
+    <t>归一化特征</t>
+  </si>
+  <si>
+    <t>2023 采集/2025 发表</t>
+  </si>
+  <si>
+    <t>同上</t>
+  </si>
+  <si>
+    <t>TMY3 典型气象年</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>2023-06 起</t>
+  </si>
+  <si>
+    <t>2023</t>
+  </si>
+  <si>
+    <t>2021</t>
+  </si>
+  <si>
+    <t>2026</t>
+  </si>
+  <si>
+    <t>2019</t>
+  </si>
+  <si>
+    <t>2025–2026</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2024-12-31</t>
+  </si>
+  <si>
+    <t>Wang et al. BurstGPT (KDD'25) github.com/HPMLL/BurstGPT</t>
+  </si>
+  <si>
+    <t>NREL TMY3 经 LBNL Modelica Buildings 库发布</t>
+  </si>
+  <si>
+    <t>Dobos NREL/TP-6A20-62641; pvlib 0.16</t>
+  </si>
+  <si>
+    <t>国家能源局西北监管局: 宁夏2025交易均价0.271 较2024同期降1.8分</t>
+  </si>
+  <si>
+    <t>国网宁夏电力 2023 信息公开年报(第三监管周期)</t>
+  </si>
+  <si>
+    <t>宁夏发改委《关于优化峰谷分时电价机制的通知》(2023-01)</t>
+  </si>
+  <si>
+    <t>同上; 峰谷价差见知乎/北极星 2024-01 汇总</t>
+  </si>
+  <si>
+    <t>Patel et al. Splitwise (ISCA'24) 表I</t>
+  </si>
+  <si>
+    <t>Patel et al. ASPLOS'24: GPU 平均占服务器功率 60%</t>
+  </si>
+  <si>
+    <t>ASPLOS'24 §4.1: 迭代间隙降至 20% TDP 即 GPU 空闲功率</t>
+  </si>
+  <si>
+    <t>ASPLOS'24 §4.2 (A100 实测)</t>
+  </si>
+  <si>
+    <t>ASPLOS'24; Splitwise ISCA'24</t>
+  </si>
+  <si>
+    <t>ASPLOS'24 POLCA 策略</t>
+  </si>
+  <si>
+    <t>NVIDIA 开发者论坛 nvidia-smi 输出; netdata 指南</t>
+  </si>
+  <si>
+    <t>Lenovo SD665-N V3 数据表(H100 700 W 最高进水 45 ℃)</t>
+  </si>
+  <si>
+    <t>ASHRAE TC9.9 第5版液冷分级(Green Grid 术语表)</t>
+  </si>
+  <si>
+    <t>Fujitsu CCLC; Asetek InRackCDU; Lenovo</t>
+  </si>
+  <si>
+    <t>ACEEE 数据中心高温液冷与热回收技术经济研究</t>
+  </si>
+  <si>
+    <t>ACEEE 2026</t>
+  </si>
+  <si>
+    <t>ASHRAE 90.1-2019 表6.8.1-3(华盛顿州法规转载)</t>
+  </si>
+  <si>
+    <t>模型假设</t>
+  </si>
+  <si>
+    <t>LiquidStack/Trane CDU-1MW: 23 kW/1350 kW</t>
+  </si>
+  <si>
+    <t>由 ASHRAE 90.1 推算</t>
+  </si>
+  <si>
+    <t>Uptime 相关报道</t>
+  </si>
+  <si>
+    <t>既有设施参数(≈25.8 m3 水当量)</t>
+  </si>
+  <si>
+    <t>工程常用值</t>
+  </si>
+  <si>
+    <t>NREL ATB 公用事业储能</t>
+  </si>
+  <si>
+    <t>与中标价格(2 h 系统)口径一致</t>
+  </si>
+  <si>
+    <t>Stojkovic et al. Microsoft Research 2026 AI-DC Lifecycle; Splitwise 表I</t>
+  </si>
+  <si>
+    <t>CPIA《中国光伏产业发展路线图(2023-2024)》(经媒体转引)</t>
+  </si>
+  <si>
+    <t>财联社; 中国能源报</t>
+  </si>
+  <si>
+    <t>SMM 2024-07</t>
+  </si>
+  <si>
+    <t>NREL ATB</t>
+  </si>
+  <si>
+    <t>ASHRAE HVAC Applications 设备中位寿命</t>
+  </si>
+  <si>
+    <t>《建设项目经济评价方法与参数》第三版(需核对原文)</t>
+  </si>
+  <si>
+    <t>CFETS 中间价(媒体转载)</t>
+  </si>
+  <si>
+    <t>案例设计值</t>
+  </si>
+  <si>
+    <t>由训练集估计</t>
+  </si>
+  <si>
+    <t>A(轨迹)/C(规模化系数)</t>
+  </si>
+  <si>
+    <t>A/C</t>
+  </si>
+  <si>
+    <t>A(数据)/C(站点替代)</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>B(表格文本提取 档位需复核)</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>A(比值)/C(移植至 H100 平均功率)</t>
+  </si>
+  <si>
+    <t>方法</t>
+  </si>
+  <si>
+    <t>式(2)</t>
+  </si>
+  <si>
+    <t>式(2)(3)</t>
+  </si>
+  <si>
+    <t>式(8)(9)</t>
+  </si>
+  <si>
+    <t>式(10)</t>
+  </si>
+  <si>
+    <t>式(16)</t>
+  </si>
+  <si>
+    <t>式(16) 敏感性</t>
+  </si>
+  <si>
+    <t>式(1)(6)</t>
+  </si>
+  <si>
+    <t>式(1)</t>
+  </si>
+  <si>
+    <t>式(1) p^sl</t>
+  </si>
+  <si>
+    <t>式(6)</t>
+  </si>
+  <si>
+    <t>式(5)(6)</t>
+  </si>
+  <si>
+    <t>式(4)(13)</t>
+  </si>
+  <si>
+    <t>式(8) φ</t>
+  </si>
+  <si>
+    <t>式(13)</t>
+  </si>
+  <si>
+    <t>式(9)(13) a^MC 标定</t>
+  </si>
+  <si>
+    <t>式(4)</t>
+  </si>
+  <si>
+    <t>式(11)</t>
+  </si>
+  <si>
+    <t>式(12)</t>
+  </si>
+  <si>
+    <t>式(15)</t>
+  </si>
+  <si>
+    <t>式(3)</t>
+  </si>
+  <si>
+    <t>式(14)</t>
+  </si>
+  <si>
+    <t>式(17)</t>
   </si>
 </sst>
 </file>
@@ -858,7 +1628,7 @@
         <v>1.250204744718339</v>
       </c>
       <c r="AD2">
-        <v>0.9738974503317253</v>
+        <v>0.9738974503317251</v>
       </c>
       <c r="AE2">
         <v>0.6841332674385543</v>
@@ -977,7 +1747,7 @@
         <v>339614.1801664073</v>
       </c>
       <c r="S3">
-        <v>188058794.4013635</v>
+        <v>188058794.4013634</v>
       </c>
       <c r="T3">
         <v>5361702.655271476</v>
@@ -989,7 +1759,7 @@
         <v>193420497.0566349</v>
       </c>
       <c r="W3">
-        <v>193671663.1288143</v>
+        <v>193671663.1288144</v>
       </c>
       <c r="X3">
         <v>193420497.0566349</v>
@@ -1010,7 +1780,7 @@
         <v>1.250225710178322</v>
       </c>
       <c r="AD3">
-        <v>0.9752158401455703</v>
+        <v>0.9752158401455704</v>
       </c>
       <c r="AE3">
         <v>0.6936511525631073</v>
@@ -1022,7 +1792,7 @@
         <v>442.1475264306681</v>
       </c>
       <c r="AH3">
-        <v>0.01820142467525068</v>
+        <v>0.0182014246752506</v>
       </c>
       <c r="AI3">
         <v>0.0158908449223583</v>
@@ -1052,7 +1822,7 @@
         <v>0.6635015139886974</v>
       </c>
       <c r="AR3">
-        <v>0.001638936028659033</v>
+        <v>0.001638936028659</v>
       </c>
       <c r="AS3">
         <v>0.3007672803850345</v>
@@ -1061,7 +1831,7 @@
         <v>-0.1146531627273517</v>
       </c>
       <c r="AU3">
-        <v>-0.1315769714978932</v>
+        <v>-0.1315769714978931</v>
       </c>
       <c r="AV3">
         <v>-3.139560796827212</v>
@@ -1186,7 +1956,7 @@
         <v>0.6857726792477142</v>
       </c>
       <c r="AI4">
-        <v>0.3142273207522858</v>
+        <v>0.3142273207522857</v>
       </c>
       <c r="AJ4">
         <v>5281804.264873045</v>
@@ -1201,7 +1971,7 @@
         <v>17011.84804288221</v>
       </c>
       <c r="AN4">
-        <v>0.06504065040650407</v>
+        <v>0.065040650406504</v>
       </c>
       <c r="AO4">
         <v>2061.57770836267</v>
@@ -1210,10 +1980,10 @@
         <v>0</v>
       </c>
       <c r="AT4">
-        <v>-0.07436003988533502</v>
+        <v>-0.074360039885335</v>
       </c>
       <c r="AU4">
-        <v>-0.07158462745352479</v>
+        <v>-0.0715846274535247</v>
       </c>
       <c r="AV4">
         <v>-2.036209560390945</v>
@@ -1222,10 +1992,10 @@
         <v>-1.129812489730642</v>
       </c>
       <c r="AX4">
-        <v>-1.052169138580727</v>
+        <v>-1.052169138580728</v>
       </c>
       <c r="AY4">
-        <v>-28.46860444680651</v>
+        <v>-28.46860444680652</v>
       </c>
       <c r="AZ4">
         <v>-1.40440889214789</v>
@@ -1269,7 +2039,7 @@
         <v>1945.984728437288</v>
       </c>
       <c r="L5">
-        <v>5.363577353380143E-14</v>
+        <v>5.363577353380144E-14</v>
       </c>
       <c r="M5">
         <v>186570911.5924677</v>
@@ -1323,7 +2093,7 @@
         <v>1.229472692381274</v>
       </c>
       <c r="AD5">
-        <v>0.9718377735061803</v>
+        <v>0.9718377735061804</v>
       </c>
       <c r="AE5">
         <v>1</v>
@@ -1335,10 +2105,10 @@
         <v>6.84640290886547E-16</v>
       </c>
       <c r="AH5">
-        <v>0.008568009132287798</v>
+        <v>0.0085680091322877</v>
       </c>
       <c r="AI5">
-        <v>0.01568456438243459</v>
+        <v>0.0156845643824345</v>
       </c>
       <c r="AJ5">
         <v>5121958.12710673</v>
@@ -1353,7 +2123,7 @@
         <v>16474.05273497376</v>
       </c>
       <c r="AN5">
-        <v>0.08130081300813008</v>
+        <v>0.08130081300813</v>
       </c>
       <c r="AO5">
         <v>6121.608306877103</v>
@@ -1365,7 +2135,7 @@
         <v>0.6732875025680989</v>
       </c>
       <c r="AR5">
-        <v>0.001741008301963829</v>
+        <v>0.0017410083019638</v>
       </c>
       <c r="AS5">
         <v>0.3007189156152151</v>
@@ -1403,7 +2173,7 @@
         <v>60</v>
       </c>
       <c r="C6">
-        <v>9997.748063236475</v>
+        <v>9997.748063236477</v>
       </c>
       <c r="D6">
         <v>408.7098033428192</v>
@@ -1496,10 +2266,10 @@
         <v>0</v>
       </c>
       <c r="AH6">
-        <v>0.01043633045144358</v>
+        <v>0.0104363304514435</v>
       </c>
       <c r="AI6">
-        <v>0.01572794277932959</v>
+        <v>0.0157279427793295</v>
       </c>
       <c r="AJ6">
         <v>5164281.187768864</v>
@@ -1514,7 +2284,7 @@
         <v>16526.71343269541</v>
       </c>
       <c r="AN6">
-        <v>0.07317073170731707</v>
+        <v>0.073170731707317</v>
       </c>
       <c r="AO6">
         <v>3604.283808296331</v>
@@ -1526,7 +2296,7 @@
         <v>0.6710286351857352</v>
       </c>
       <c r="AR6">
-        <v>0.001271709705632322</v>
+        <v>0.0012717097056323</v>
       </c>
       <c r="AS6">
         <v>0.3015353818778593</v>
@@ -1657,10 +2427,10 @@
         <v>0</v>
       </c>
       <c r="AH7">
-        <v>0.009160178215470126</v>
+        <v>0.0091601782154701</v>
       </c>
       <c r="AI7">
-        <v>0.01570443184776726</v>
+        <v>0.0157044318477672</v>
       </c>
       <c r="AJ7">
         <v>5161979.979526302</v>
@@ -1675,7 +2445,7 @@
         <v>16525.25077720819</v>
       </c>
       <c r="AN7">
-        <v>0.08130081300813008</v>
+        <v>0.08130081300813</v>
       </c>
       <c r="AO7">
         <v>6441.490330749621</v>
@@ -1687,16 +2457,16 @@
         <v>0.6728655184035998</v>
       </c>
       <c r="AR7">
-        <v>0.001201447950946774</v>
+        <v>0.0012014479509467</v>
       </c>
       <c r="AS7">
         <v>0.3010684235822161</v>
       </c>
       <c r="AT7">
-        <v>-0.3263551624966388</v>
+        <v>-0.3263551624966387</v>
       </c>
       <c r="AU7">
-        <v>-0.3406427068499807</v>
+        <v>-0.3406427068499806</v>
       </c>
       <c r="AV7">
         <v>-8.936621107026877</v>
@@ -1728,7 +2498,7 @@
         <v>205446.134967953</v>
       </c>
       <c r="D8">
-        <v>902.0369598865509</v>
+        <v>902.0369598865508</v>
       </c>
       <c r="E8">
         <v>24170</v>
@@ -1785,7 +2555,7 @@
         <v>193195875.5942996</v>
       </c>
       <c r="W8">
-        <v>193966570.2333099</v>
+        <v>193966570.2333098</v>
       </c>
       <c r="X8">
         <v>193475476.875027</v>
@@ -1818,10 +2588,10 @@
         <v>25.22508564951047</v>
       </c>
       <c r="AH8">
-        <v>0.007912442773929806</v>
+        <v>0.007912442773929799</v>
       </c>
       <c r="AI8">
-        <v>0.01558131230933775</v>
+        <v>0.0155813123093377</v>
       </c>
       <c r="AJ8">
         <v>5172432.208158784</v>
@@ -1836,7 +2606,7 @@
         <v>16533.84475880678</v>
       </c>
       <c r="AN8">
-        <v>0.05691056910569105</v>
+        <v>0.056910569105691</v>
       </c>
       <c r="AO8">
         <v>754.6993326474067</v>
@@ -1848,16 +2618,16 @@
         <v>0.6739438427036031</v>
       </c>
       <c r="AR8">
-        <v>0.001404246134484554</v>
+        <v>0.0014042461344845</v>
       </c>
       <c r="AS8">
-        <v>0.3011581560786448</v>
+        <v>0.3011581560786447</v>
       </c>
       <c r="AT8">
         <v>-0.2306511723172533</v>
       </c>
       <c r="AU8">
-        <v>0.02049435886641859</v>
+        <v>0.0204943588664185</v>
       </c>
       <c r="AV8">
         <v>-6.315947690614676</v>
@@ -1999,7 +2769,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>6.039613253960852E-13</v>
+        <v>6.039613253960853E-13</v>
       </c>
       <c r="E3">
         <v>2.771116669464391E-13</v>
@@ -2093,7 +2863,7 @@
         <v>3</v>
       </c>
       <c r="D5">
-        <v>5.968558980384842E-13</v>
+        <v>5.968558980384843E-13</v>
       </c>
       <c r="E5">
         <v>5.329070518200751E-13</v>
@@ -2140,7 +2910,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>6.536993168992922E-13</v>
+        <v>6.536993168992923E-13</v>
       </c>
       <c r="E6">
         <v>2.273736754432321E-13</v>
@@ -2234,7 +3004,7 @@
         <v>1</v>
       </c>
       <c r="D8">
-        <v>6.536993168992922E-13</v>
+        <v>6.536993168992923E-13</v>
       </c>
       <c r="E8">
         <v>2.842170943040401E-13</v>
@@ -2281,7 +3051,7 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>6.252776074688882E-13</v>
+        <v>6.252776074688883E-13</v>
       </c>
       <c r="E9">
         <v>6.821210263296962E-13</v>
@@ -2422,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="D12">
-        <v>5.826450433232822E-13</v>
+        <v>5.826450433232823E-13</v>
       </c>
       <c r="E12">
         <v>2.273736754432321E-13</v>
@@ -2516,7 +3286,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>5.790923296444817E-13</v>
+        <v>5.790923296444818E-13</v>
       </c>
       <c r="E14">
         <v>2.273736754432321E-13</v>
@@ -2751,7 +3521,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>5.383672052362418E-13</v>
+        <v>5.383672052362419E-13</v>
       </c>
       <c r="E19">
         <v>2.842170943040401E-13</v>
@@ -2939,10 +3709,10 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>6.679101716144942E-13</v>
+        <v>6.679101716144943E-13</v>
       </c>
       <c r="E23">
-        <v>1.4210854715202E-13</v>
+        <v>1.421085471520201E-13</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -2986,7 +3756,7 @@
         <v>2</v>
       </c>
       <c r="D24">
-        <v>6.608047442568932E-13</v>
+        <v>6.608047442568933E-13</v>
       </c>
       <c r="E24">
         <v>2.273736754432321E-13</v>
@@ -3033,7 +3803,7 @@
         <v>3</v>
       </c>
       <c r="D25">
-        <v>6.252776074688882E-13</v>
+        <v>6.252776074688883E-13</v>
       </c>
       <c r="E25">
         <v>2.273736754432321E-13</v>
@@ -3083,7 +3853,7 @@
         <v>4.121147867408581E-13</v>
       </c>
       <c r="E26">
-        <v>1.13686837721616E-13</v>
+        <v>1.136868377216161E-13</v>
       </c>
       <c r="H26">
         <v>0</v>
@@ -3221,7 +3991,7 @@
         <v>2</v>
       </c>
       <c r="D29">
-        <v>6.394884621840902E-13</v>
+        <v>6.394884621840903E-13</v>
       </c>
       <c r="E29">
         <v>2.273736754432321E-13</v>
@@ -3315,7 +4085,7 @@
         <v>4</v>
       </c>
       <c r="D31">
-        <v>6.536993168992922E-13</v>
+        <v>6.536993168992923E-13</v>
       </c>
       <c r="E31">
         <v>2.273736754432321E-13</v>
@@ -3362,7 +4132,7 @@
         <v>0</v>
       </c>
       <c r="D32">
-        <v>5.755396159656812E-13</v>
+        <v>5.755396159656813E-13</v>
       </c>
       <c r="E32">
         <v>2.273736754432321E-13</v>
@@ -3412,7 +4182,7 @@
         <v>5.400124791776761E-13</v>
       </c>
       <c r="E33">
-        <v>1.20792265079217E-13</v>
+        <v>1.207922650792171E-13</v>
       </c>
       <c r="H33">
         <v>0</v>
@@ -3521,7 +4291,7 @@
         <v>68.69413756991797</v>
       </c>
       <c r="L35">
-        <v>-93.25436663059781</v>
+        <v>-93.2543666305978</v>
       </c>
       <c r="M35">
         <v>0</v>
@@ -3600,7 +4370,7 @@
         <v>8.881784197001252E-13</v>
       </c>
       <c r="E37">
-        <v>1.4210854715202E-13</v>
+        <v>1.421085471520201E-13</v>
       </c>
       <c r="H37">
         <v>0</v>
@@ -3741,7 +4511,7 @@
         <v>5.044853423896711E-13</v>
       </c>
       <c r="E40">
-        <v>1.13686837721616E-13</v>
+        <v>1.136868377216161E-13</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -4023,7 +4793,7 @@
         <v>4.618527782440651E-13</v>
       </c>
       <c r="E46">
-        <v>1.250555214937776E-12</v>
+        <v>1.250555214937777E-12</v>
       </c>
       <c r="H46">
         <v>0</v>
@@ -4144,7 +4914,7 @@
         <v>9.094947017729282E-13</v>
       </c>
       <c r="P48">
-        <v>28.46086522705646</v>
+        <v>28.46086522705645</v>
       </c>
       <c r="Q48">
         <v>45.00000000000004</v>
@@ -4161,7 +4931,7 @@
         <v>2</v>
       </c>
       <c r="D49">
-        <v>6.679101716144942E-13</v>
+        <v>6.679101716144943E-13</v>
       </c>
       <c r="E49">
         <v>3.566924533515703E-12</v>
@@ -4191,7 +4961,7 @@
         <v>0</v>
       </c>
       <c r="P49">
-        <v>31.99999999999999</v>
+        <v>32</v>
       </c>
       <c r="Q49">
         <v>45</v>
@@ -4285,7 +5055,7 @@
         <v>0</v>
       </c>
       <c r="P51">
-        <v>31.99999999999999</v>
+        <v>31.99999999999998</v>
       </c>
       <c r="Q51">
         <v>45</v>
@@ -4302,7 +5072,7 @@
         <v>0</v>
       </c>
       <c r="D52">
-        <v>6.572520305780927E-13</v>
+        <v>6.572520305780928E-13</v>
       </c>
       <c r="E52">
         <v>7.389644451905042E-13</v>
@@ -4493,7 +5263,7 @@
         <v>2.913225216616411E-13</v>
       </c>
       <c r="E56">
-        <v>6.536993168992922E-13</v>
+        <v>6.536993168992923E-13</v>
       </c>
       <c r="H56">
         <v>0</v>
@@ -4540,7 +5310,7 @@
         <v>5.044853423896711E-13</v>
       </c>
       <c r="E57">
-        <v>1.307398633798584E-12</v>
+        <v>1.307398633798585E-12</v>
       </c>
       <c r="H57">
         <v>0</v>
@@ -4587,7 +5357,7 @@
         <v>2.913225216616411E-13</v>
       </c>
       <c r="E58">
-        <v>6.252776074688882E-13</v>
+        <v>6.252776074688883E-13</v>
       </c>
       <c r="H58">
         <v>0</v>
@@ -4631,7 +5401,7 @@
         <v>2</v>
       </c>
       <c r="D59">
-        <v>6.679101716144942E-13</v>
+        <v>6.679101716144943E-13</v>
       </c>
       <c r="E59">
         <v>5.542233338928781E-13</v>
@@ -4681,7 +5451,7 @@
         <v>3.197442310920451E-13</v>
       </c>
       <c r="E60">
-        <v>5.968558980384842E-13</v>
+        <v>5.968558980384843E-13</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -4725,7 +5495,7 @@
         <v>4</v>
       </c>
       <c r="D61">
-        <v>6.181721801112872E-13</v>
+        <v>6.181721801112873E-13</v>
       </c>
       <c r="E61">
         <v>2.557953848736361E-13</v>
@@ -4799,10 +5569,10 @@
         <v>0</v>
       </c>
       <c r="O62">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P62">
-        <v>24.99999999999999</v>
+        <v>25</v>
       </c>
       <c r="Q62">
         <v>50.00000000000001</v>
@@ -4893,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="O64">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P64">
         <v>25</v>
@@ -4940,7 +5710,7 @@
         <v>0</v>
       </c>
       <c r="O65">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P65">
         <v>25</v>
@@ -5034,7 +5804,7 @@
         <v>0</v>
       </c>
       <c r="O67">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P67">
         <v>25</v>
@@ -5081,7 +5851,7 @@
         <v>0</v>
       </c>
       <c r="O68">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P68">
         <v>25</v>
@@ -5166,7 +5936,7 @@
         <v>84.80000000000001</v>
       </c>
       <c r="L70">
-        <v>-227.6590162718355</v>
+        <v>-227.6590162718356</v>
       </c>
       <c r="M70">
         <v>0</v>
@@ -5195,7 +5965,7 @@
         <v>4</v>
       </c>
       <c r="D71">
-        <v>6.536993168992922E-13</v>
+        <v>6.536993168992923E-13</v>
       </c>
       <c r="E71">
         <v>2.273736754432321E-13</v>
@@ -5269,7 +6039,7 @@
         <v>0</v>
       </c>
       <c r="O72">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P72">
         <v>25</v>
@@ -5316,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="O73">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P73">
         <v>25</v>
@@ -5336,7 +6106,7 @@
         <v>2</v>
       </c>
       <c r="D74">
-        <v>5.826450433232822E-13</v>
+        <v>5.826450433232823E-13</v>
       </c>
       <c r="E74">
         <v>4.405364961712621E-13</v>
@@ -5366,7 +6136,7 @@
         <v>2.273736754432321E-13</v>
       </c>
       <c r="P74">
-        <v>24.99999999999999</v>
+        <v>25</v>
       </c>
       <c r="Q74">
         <v>50</v>
@@ -5524,7 +6294,7 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>6.323830348264892E-13</v>
+        <v>6.323830348264893E-13</v>
       </c>
       <c r="E78">
         <v>2.273736754432321E-13</v>
@@ -5551,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="O78">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P78">
         <v>25</v>
@@ -5598,7 +6368,7 @@
         <v>0</v>
       </c>
       <c r="O79">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P79">
         <v>25</v>
@@ -5645,7 +6415,7 @@
         <v>0</v>
       </c>
       <c r="O80">
-        <v>-5.363577353380143E-14</v>
+        <v>-5.363577353380144E-14</v>
       </c>
       <c r="P80">
         <v>25</v>
@@ -5759,7 +6529,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>6.252776074688882E-13</v>
+        <v>6.252776074688883E-13</v>
       </c>
       <c r="E83">
         <v>2.273736754432321E-13</v>
@@ -5900,7 +6670,7 @@
         <v>4</v>
       </c>
       <c r="D86">
-        <v>6.679101716144942E-13</v>
+        <v>6.679101716144943E-13</v>
       </c>
       <c r="E86">
         <v>2.842170943040401E-13</v>
@@ -5994,7 +6764,7 @@
         <v>1</v>
       </c>
       <c r="D88">
-        <v>5.968558980384842E-13</v>
+        <v>5.968558980384843E-13</v>
       </c>
       <c r="E88">
         <v>2.273736754432321E-13</v>
@@ -6041,7 +6811,7 @@
         <v>2</v>
       </c>
       <c r="D89">
-        <v>6.679101716144942E-13</v>
+        <v>6.679101716144943E-13</v>
       </c>
       <c r="E89">
         <v>4.547473508864641E-13</v>
@@ -6435,7 +7205,7 @@
         <v>84.80000000000001</v>
       </c>
       <c r="L97">
-        <v>-227.6590162718355</v>
+        <v>-227.6590162718356</v>
       </c>
       <c r="M97">
         <v>0</v>
@@ -6699,7 +7469,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>6.252776074688882E-13</v>
+        <v>6.252776074688883E-13</v>
       </c>
       <c r="E103">
         <v>2.273736754432321E-13</v>
@@ -6840,7 +7610,7 @@
         <v>4</v>
       </c>
       <c r="D106">
-        <v>6.750155989720952E-13</v>
+        <v>6.750155989720953E-13</v>
       </c>
       <c r="E106">
         <v>3.979039320256561E-13</v>
@@ -6981,7 +7751,7 @@
         <v>2</v>
       </c>
       <c r="D109">
-        <v>6.679101716144942E-13</v>
+        <v>6.679101716144943E-13</v>
       </c>
       <c r="E109">
         <v>4.263256414560601E-13</v>
@@ -7122,7 +7892,7 @@
         <v>0</v>
       </c>
       <c r="D112">
-        <v>5.968558980384842E-13</v>
+        <v>5.968558980384843E-13</v>
       </c>
       <c r="E112">
         <v>2.273736754432321E-13</v>
@@ -7375,7 +8145,7 @@
         <v>84.80000000000001</v>
       </c>
       <c r="L117">
-        <v>-227.6590162718355</v>
+        <v>-227.6590162718356</v>
       </c>
       <c r="M117">
         <v>0</v>
@@ -8092,7 +8862,7 @@
         <v>4.547473508864641E-13</v>
       </c>
       <c r="P132">
-        <v>24.99999999999999</v>
+        <v>24.99999999999998</v>
       </c>
       <c r="Q132">
         <v>50</v>
@@ -8156,7 +8926,7 @@
         <v>4</v>
       </c>
       <c r="D134">
-        <v>6.110667527536862E-13</v>
+        <v>6.110667527536863E-13</v>
       </c>
       <c r="E134">
         <v>4.547473508864641E-13</v>
@@ -8438,7 +9208,7 @@
         <v>2</v>
       </c>
       <c r="D140">
-        <v>6.536993168992922E-13</v>
+        <v>6.536993168992923E-13</v>
       </c>
       <c r="E140">
         <v>3.865352482534945E-12</v>
@@ -8579,7 +9349,7 @@
         <v>5</v>
       </c>
       <c r="D143">
-        <v>5.826450433232822E-13</v>
+        <v>5.826450433232823E-13</v>
       </c>
       <c r="E143">
         <v>1.818989403545856E-12</v>
@@ -8609,7 +9379,7 @@
         <v>6.821210263296962E-13</v>
       </c>
       <c r="P143">
-        <v>24.99999999999999</v>
+        <v>25</v>
       </c>
       <c r="Q143">
         <v>45.00000000000001</v>
@@ -9140,7 +9910,7 @@
         <v>1</v>
       </c>
       <c r="D3">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E3">
         <v>0.2354829867415565</v>
@@ -9177,7 +9947,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E5">
-        <v>0.2597048779422245</v>
+        <v>0.2597048779422244</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -9191,7 +9961,7 @@
         <v>4</v>
       </c>
       <c r="D6">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E6">
         <v>0.0743194049342277</v>
@@ -9211,7 +9981,7 @@
         <v>0.2622950819672131</v>
       </c>
       <c r="E7">
-        <v>0.03414430873925169</v>
+        <v>0.0341443087392516</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -9310,7 +10080,7 @@
         <v>1</v>
       </c>
       <c r="D13">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E13">
         <v>0.2120448603086426</v>
@@ -9327,7 +10097,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E14">
         <v>0.1906590281912955</v>
@@ -9344,7 +10114,7 @@
         <v>3</v>
       </c>
       <c r="D15">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -9361,7 +10131,7 @@
         <v>4</v>
       </c>
       <c r="D16">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -9395,7 +10165,7 @@
         <v>1</v>
       </c>
       <c r="D18">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E18">
         <v>0.2027573338717642</v>
@@ -9412,7 +10182,7 @@
         <v>2</v>
       </c>
       <c r="D19">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E19">
         <v>0.2061532204219035</v>
@@ -9480,7 +10250,7 @@
         <v>1</v>
       </c>
       <c r="D23">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E23">
         <v>0.2354829867415565</v>
@@ -9517,7 +10287,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E25">
-        <v>0.2597048779422245</v>
+        <v>0.2597048779422244</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -9531,7 +10301,7 @@
         <v>4</v>
       </c>
       <c r="D26">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E26">
         <v>0.0743194049342277</v>
@@ -9551,7 +10321,7 @@
         <v>0.2622950819672131</v>
       </c>
       <c r="E27">
-        <v>0.03414430873925169</v>
+        <v>0.0341443087392516</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -9650,10 +10420,10 @@
         <v>1</v>
       </c>
       <c r="D33">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E33">
-        <v>0.1582446487955904</v>
+        <v>0.1582446487955903</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -9667,7 +10437,7 @@
         <v>2</v>
       </c>
       <c r="D34">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E34">
         <v>0.1695280942825858</v>
@@ -9684,7 +10454,7 @@
         <v>3</v>
       </c>
       <c r="D35">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -9701,10 +10471,10 @@
         <v>4</v>
       </c>
       <c r="D36">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E36">
-        <v>0.05834926883338756</v>
+        <v>0.0583492688333875</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -9735,7 +10505,7 @@
         <v>1</v>
       </c>
       <c r="D38">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E38">
         <v>0.2027573338717642</v>
@@ -9752,7 +10522,7 @@
         <v>2</v>
       </c>
       <c r="D39">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E39">
         <v>0.2061532204219035</v>
@@ -9820,7 +10590,7 @@
         <v>1</v>
       </c>
       <c r="D43">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E43">
         <v>0.2354829867415565</v>
@@ -9857,7 +10627,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E45">
-        <v>0.2597048779422245</v>
+        <v>0.2597048779422244</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -9871,7 +10641,7 @@
         <v>4</v>
       </c>
       <c r="D46">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E46">
         <v>0.0743194049342277</v>
@@ -9925,7 +10695,7 @@
         <v>0.1147540983606557</v>
       </c>
       <c r="E49">
-        <v>0.4279562359463974</v>
+        <v>0.4279562359463973</v>
       </c>
     </row>
     <row r="50" spans="1:5">
@@ -9942,7 +10712,7 @@
         <v>0.1967213114754098</v>
       </c>
       <c r="E50">
-        <v>0.2696998711982773</v>
+        <v>0.2696998711982772</v>
       </c>
     </row>
     <row r="51" spans="1:5">
@@ -9990,10 +10760,10 @@
         <v>1</v>
       </c>
       <c r="D53">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E53">
-        <v>0.1582446487955904</v>
+        <v>0.1582446487955903</v>
       </c>
     </row>
     <row r="54" spans="1:5">
@@ -10007,7 +10777,7 @@
         <v>2</v>
       </c>
       <c r="D54">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E54">
         <v>0.1695280942825858</v>
@@ -10024,7 +10794,7 @@
         <v>3</v>
       </c>
       <c r="D55">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -10041,10 +10811,10 @@
         <v>4</v>
       </c>
       <c r="D56">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E56">
-        <v>0.05834926883338756</v>
+        <v>0.0583492688333875</v>
       </c>
     </row>
     <row r="57" spans="1:5">
@@ -10075,7 +10845,7 @@
         <v>1</v>
       </c>
       <c r="D58">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E58">
         <v>0.2027573338717642</v>
@@ -10092,7 +10862,7 @@
         <v>2</v>
       </c>
       <c r="D59">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E59">
         <v>0.2061532204219035</v>
@@ -10160,7 +10930,7 @@
         <v>1</v>
       </c>
       <c r="D63">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E63">
         <v>0.2354829867415565</v>
@@ -10197,7 +10967,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E65">
-        <v>0.2597048779422245</v>
+        <v>0.2597048779422244</v>
       </c>
     </row>
     <row r="66" spans="1:5">
@@ -10211,7 +10981,7 @@
         <v>4</v>
       </c>
       <c r="D66">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E66">
         <v>0.0743194049342277</v>
@@ -10265,7 +11035,7 @@
         <v>0.1147540983606557</v>
       </c>
       <c r="E69">
-        <v>0.4279562359463974</v>
+        <v>0.4279562359463973</v>
       </c>
     </row>
     <row r="70" spans="1:5">
@@ -10282,7 +11052,7 @@
         <v>0.1967213114754098</v>
       </c>
       <c r="E70">
-        <v>0.2696998711982773</v>
+        <v>0.2696998711982772</v>
       </c>
     </row>
     <row r="71" spans="1:5">
@@ -10330,10 +11100,10 @@
         <v>1</v>
       </c>
       <c r="D73">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E73">
-        <v>0.1582446487955904</v>
+        <v>0.1582446487955903</v>
       </c>
     </row>
     <row r="74" spans="1:5">
@@ -10347,7 +11117,7 @@
         <v>2</v>
       </c>
       <c r="D74">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E74">
         <v>0.1695280942825858</v>
@@ -10364,7 +11134,7 @@
         <v>3</v>
       </c>
       <c r="D75">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -10381,10 +11151,10 @@
         <v>4</v>
       </c>
       <c r="D76">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E76">
-        <v>0.05834926883338756</v>
+        <v>0.0583492688333875</v>
       </c>
     </row>
     <row r="77" spans="1:5">
@@ -10415,7 +11185,7 @@
         <v>1</v>
       </c>
       <c r="D78">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E78">
         <v>0.2027573338717642</v>
@@ -10432,7 +11202,7 @@
         <v>2</v>
       </c>
       <c r="D79">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E79">
         <v>0.2061532204219035</v>
@@ -10500,7 +11270,7 @@
         <v>1</v>
       </c>
       <c r="D83">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E83">
         <v>0.2354829867415565</v>
@@ -10537,7 +11307,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E85">
-        <v>0.2597048779422245</v>
+        <v>0.2597048779422244</v>
       </c>
     </row>
     <row r="86" spans="1:5">
@@ -10551,7 +11321,7 @@
         <v>4</v>
       </c>
       <c r="D86">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E86">
         <v>0.0743194049342277</v>
@@ -10605,7 +11375,7 @@
         <v>0.1147540983606557</v>
       </c>
       <c r="E89">
-        <v>0.4279562359463974</v>
+        <v>0.4279562359463973</v>
       </c>
     </row>
     <row r="90" spans="1:5">
@@ -10622,7 +11392,7 @@
         <v>0.1967213114754098</v>
       </c>
       <c r="E90">
-        <v>0.2696998711982773</v>
+        <v>0.2696998711982772</v>
       </c>
     </row>
     <row r="91" spans="1:5">
@@ -10670,10 +11440,10 @@
         <v>1</v>
       </c>
       <c r="D93">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E93">
-        <v>0.1582446487955904</v>
+        <v>0.1582446487955903</v>
       </c>
     </row>
     <row r="94" spans="1:5">
@@ -10687,7 +11457,7 @@
         <v>2</v>
       </c>
       <c r="D94">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E94">
         <v>0.1695280942825858</v>
@@ -10704,7 +11474,7 @@
         <v>3</v>
       </c>
       <c r="D95">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -10721,10 +11491,10 @@
         <v>4</v>
       </c>
       <c r="D96">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E96">
-        <v>0.05834926883338756</v>
+        <v>0.0583492688333875</v>
       </c>
     </row>
     <row r="97" spans="1:5">
@@ -10755,7 +11525,7 @@
         <v>1</v>
       </c>
       <c r="D98">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E98">
         <v>0.2027573338717642</v>
@@ -10772,7 +11542,7 @@
         <v>2</v>
       </c>
       <c r="D99">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E99">
         <v>0.2061532204219035</v>
@@ -10840,7 +11610,7 @@
         <v>1</v>
       </c>
       <c r="D103">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E103">
         <v>0.2354829867415565</v>
@@ -10877,7 +11647,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E105">
-        <v>0.2597048779422245</v>
+        <v>0.2597048779422244</v>
       </c>
     </row>
     <row r="106" spans="1:5">
@@ -10891,7 +11661,7 @@
         <v>4</v>
       </c>
       <c r="D106">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E106">
         <v>0.0743194049342277</v>
@@ -10945,7 +11715,7 @@
         <v>0.1147540983606557</v>
       </c>
       <c r="E109">
-        <v>0.4279562359463974</v>
+        <v>0.4279562359463973</v>
       </c>
     </row>
     <row r="110" spans="1:5">
@@ -10962,7 +11732,7 @@
         <v>0.1967213114754098</v>
       </c>
       <c r="E110">
-        <v>0.2696998711982773</v>
+        <v>0.2696998711982772</v>
       </c>
     </row>
     <row r="111" spans="1:5">
@@ -11010,10 +11780,10 @@
         <v>1</v>
       </c>
       <c r="D113">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E113">
-        <v>0.1582446487955904</v>
+        <v>0.1582446487955903</v>
       </c>
     </row>
     <row r="114" spans="1:5">
@@ -11027,7 +11797,7 @@
         <v>2</v>
       </c>
       <c r="D114">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E114">
         <v>0.1695280942825858</v>
@@ -11044,7 +11814,7 @@
         <v>3</v>
       </c>
       <c r="D115">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -11061,10 +11831,10 @@
         <v>4</v>
       </c>
       <c r="D116">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E116">
-        <v>0.05834926883338756</v>
+        <v>0.0583492688333875</v>
       </c>
     </row>
     <row r="117" spans="1:5">
@@ -11095,7 +11865,7 @@
         <v>1</v>
       </c>
       <c r="D118">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E118">
         <v>0.2027573338717642</v>
@@ -11112,7 +11882,7 @@
         <v>2</v>
       </c>
       <c r="D119">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E119">
         <v>0.2061532204219035</v>
@@ -11180,7 +11950,7 @@
         <v>1</v>
       </c>
       <c r="D123">
-        <v>0.1475409836065574</v>
+        <v>0.1475409836065573</v>
       </c>
       <c r="E123">
         <v>0.2434518928804708</v>
@@ -11217,7 +11987,7 @@
         <v>0.360655737704918</v>
       </c>
       <c r="E125">
-        <v>0.02394834444520645</v>
+        <v>0.0239483444452064</v>
       </c>
     </row>
     <row r="126" spans="1:5">
@@ -11231,7 +12001,7 @@
         <v>4</v>
       </c>
       <c r="D126">
-        <v>0.04918032786885246</v>
+        <v>0.0491803278688524</v>
       </c>
       <c r="E126">
         <v>0</v>
@@ -11387,7 +12157,7 @@
         <v>0</v>
       </c>
       <c r="E135">
-        <v>0.1661623605842701</v>
+        <v>0.16616236058427</v>
       </c>
     </row>
     <row r="136" spans="1:5">
@@ -11404,7 +12174,7 @@
         <v>0</v>
       </c>
       <c r="E136">
-        <v>0.06862270628837742</v>
+        <v>0.0686227062883774</v>
       </c>
     </row>
     <row r="137" spans="1:5">
@@ -11421,7 +12191,7 @@
         <v>0</v>
       </c>
       <c r="E137">
-        <v>0.1209827805652759</v>
+        <v>0.1209827805652758</v>
       </c>
     </row>
     <row r="138" spans="1:5">
@@ -11452,7 +12222,7 @@
         <v>1</v>
       </c>
       <c r="D139">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -11469,7 +12239,7 @@
         <v>2</v>
       </c>
       <c r="D140">
-        <v>0.06666666666666667</v>
+        <v>0.0666666666666666</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -11486,7 +12256,7 @@
         <v>3</v>
       </c>
       <c r="D141">
-        <v>0.2666666666666667</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -11503,7 +12273,7 @@
         <v>4</v>
       </c>
       <c r="D142">
-        <v>0.1666666666666667</v>
+        <v>0.1666666666666666</v>
       </c>
       <c r="E142">
         <v>0.2582466675919974</v>
@@ -11540,7 +12310,7 @@
         <v>0</v>
       </c>
       <c r="E144">
-        <v>0.2556934010257461</v>
+        <v>0.255693401025746</v>
       </c>
     </row>
     <row r="145" spans="1:5">
@@ -11588,7 +12358,7 @@
         <v>1</v>
       </c>
       <c r="D147">
-        <v>0.2203389830508475</v>
+        <v>0.2203389830508474</v>
       </c>
       <c r="E147">
         <v>0.271812321896512</v>
@@ -11605,7 +12375,7 @@
         <v>2</v>
       </c>
       <c r="D148">
-        <v>0.1355932203389831</v>
+        <v>0.135593220338983</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -11625,7 +12395,7 @@
         <v>0.288135593220339</v>
       </c>
       <c r="E149">
-        <v>0.02275528127372719</v>
+        <v>0.0227552812737271</v>
       </c>
     </row>
     <row r="150" spans="1:5">
@@ -11659,7 +12429,7 @@
         <v>0</v>
       </c>
       <c r="E151">
-        <v>0.1020668561324255</v>
+        <v>0.1020668561324254</v>
       </c>
     </row>
     <row r="152" spans="1:5">
@@ -11693,7 +12463,3464 @@
         <v>0</v>
       </c>
       <c r="E153">
-        <v>0.1436078890137777</v>
+        <v>0.1436078890137776</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:AN17"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:40">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="2" spans="1:40">
+      <c r="A2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C2">
+        <v>5488.738021939993</v>
+      </c>
+      <c r="D2">
+        <v>268.8412897586823</v>
+      </c>
+      <c r="E2">
+        <v>15134</v>
+      </c>
+      <c r="F2">
+        <v>23061</v>
+      </c>
+      <c r="G2">
+        <v>2099</v>
+      </c>
+      <c r="H2">
+        <v>3088.397125915816</v>
+      </c>
+      <c r="I2">
+        <v>-0</v>
+      </c>
+      <c r="J2">
+        <v>-0</v>
+      </c>
+      <c r="K2">
+        <v>1930.426268505075</v>
+      </c>
+      <c r="L2">
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N2">
+        <v>1060632.603235957</v>
+      </c>
+      <c r="O2">
+        <v>-0</v>
+      </c>
+      <c r="P2">
+        <v>-0</v>
+      </c>
+      <c r="Q2">
+        <v>106093.1793926889</v>
+      </c>
+      <c r="R2">
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <v>187737637.3750963</v>
+      </c>
+      <c r="T2">
+        <v>5272280.340753082</v>
+      </c>
+      <c r="U2">
+        <v>5272280.340753082</v>
+      </c>
+      <c r="V2">
+        <v>193009917.7158494</v>
+      </c>
+      <c r="W2">
+        <v>193009917.7158494</v>
+      </c>
+      <c r="X2">
+        <v>193011454.25448</v>
+      </c>
+      <c r="Y2">
+        <v>6439006.123381728</v>
+      </c>
+      <c r="Z2">
+        <v>14215.99594997134</v>
+      </c>
+      <c r="AA2">
+        <v>17478.13259823352</v>
+      </c>
+      <c r="AB2">
+        <v>12814.08398902585</v>
+      </c>
+      <c r="AC2">
+        <v>1.229469441306977</v>
+      </c>
+      <c r="AD2">
+        <v>0.972149761160172</v>
+      </c>
+      <c r="AE2">
+        <v>1</v>
+      </c>
+      <c r="AF2">
+        <v>479.7898633115327</v>
+      </c>
+      <c r="AG2">
+        <v>0</v>
+      </c>
+      <c r="AH2">
+        <v>0.012600256342995</v>
+      </c>
+      <c r="AI2">
+        <v>0.6689410463886885</v>
+      </c>
+      <c r="AJ2">
+        <v>0.015728025921625</v>
+      </c>
+      <c r="AK2">
+        <v>0.0006776963684125</v>
+      </c>
+      <c r="AL2">
+        <v>0.3020529749782791</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:40">
+      <c r="A3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C3">
+        <v>9463.804320722818</v>
+      </c>
+      <c r="D3">
+        <v>256.9182977676392</v>
+      </c>
+      <c r="E3">
+        <v>15134</v>
+      </c>
+      <c r="F3">
+        <v>23061</v>
+      </c>
+      <c r="G3">
+        <v>2099</v>
+      </c>
+      <c r="H3">
+        <v>3050.755943705856</v>
+      </c>
+      <c r="I3">
+        <v>-0</v>
+      </c>
+      <c r="J3">
+        <v>-0</v>
+      </c>
+      <c r="K3">
+        <v>1930.426268505075</v>
+      </c>
+      <c r="L3">
+        <v>-0</v>
+      </c>
+      <c r="M3">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N3">
+        <v>1047705.682426059</v>
+      </c>
+      <c r="O3">
+        <v>-0</v>
+      </c>
+      <c r="P3">
+        <v>-0</v>
+      </c>
+      <c r="Q3">
+        <v>106093.1793926889</v>
+      </c>
+      <c r="R3">
+        <v>-0</v>
+      </c>
+      <c r="S3">
+        <v>187724710.4542864</v>
+      </c>
+      <c r="T3">
+        <v>5285232.322383704</v>
+      </c>
+      <c r="U3">
+        <v>5412004.482700269</v>
+      </c>
+      <c r="V3">
+        <v>193009942.7766701</v>
+      </c>
+      <c r="W3">
+        <v>193136714.9369867</v>
+      </c>
+      <c r="X3">
+        <v>193137232.5661096</v>
+      </c>
+      <c r="Y3">
+        <v>6439031.184202451</v>
+      </c>
+      <c r="Z3">
+        <v>14215.14258677511</v>
+      </c>
+      <c r="AA3">
+        <v>17477.09918971948</v>
+      </c>
+      <c r="AB3">
+        <v>12860.45828677262</v>
+      </c>
+      <c r="AC3">
+        <v>1.229470551071299</v>
+      </c>
+      <c r="AD3">
+        <v>0.9741411164366144</v>
+      </c>
+      <c r="AE3">
+        <v>1</v>
+      </c>
+      <c r="AF3">
+        <v>479.7610623036598</v>
+      </c>
+      <c r="AG3">
+        <v>0</v>
+      </c>
+      <c r="AH3">
+        <v>0.0108511358858026</v>
+      </c>
+      <c r="AI3">
+        <v>0.6706997573998027</v>
+      </c>
+      <c r="AJ3">
+        <v>0.0157304278234031</v>
+      </c>
+      <c r="AK3">
+        <v>0.000179043766688</v>
+      </c>
+      <c r="AL3">
+        <v>0.3025396351243035</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN3">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:40">
+      <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C4">
+        <v>8643.621705830097</v>
+      </c>
+      <c r="D4">
+        <v>445.2698202133178</v>
+      </c>
+      <c r="E4">
+        <v>15134</v>
+      </c>
+      <c r="F4">
+        <v>23061</v>
+      </c>
+      <c r="G4">
+        <v>2099</v>
+      </c>
+      <c r="H4">
+        <v>2912.952801778904</v>
+      </c>
+      <c r="I4">
+        <v>-0</v>
+      </c>
+      <c r="J4">
+        <v>-0</v>
+      </c>
+      <c r="K4">
+        <v>2013.85397513202</v>
+      </c>
+      <c r="L4">
+        <v>-0</v>
+      </c>
+      <c r="M4">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N4">
+        <v>1000380.646429357</v>
+      </c>
+      <c r="O4">
+        <v>-0</v>
+      </c>
+      <c r="P4">
+        <v>-0</v>
+      </c>
+      <c r="Q4">
+        <v>110678.234408723</v>
+      </c>
+      <c r="R4">
+        <v>-0</v>
+      </c>
+      <c r="S4">
+        <v>187681970.4733057</v>
+      </c>
+      <c r="T4">
+        <v>5333275.724114026</v>
+      </c>
+      <c r="U4">
+        <v>5830850.800425679</v>
+      </c>
+      <c r="V4">
+        <v>193015246.1974198</v>
+      </c>
+      <c r="W4">
+        <v>193512821.2737314</v>
+      </c>
+      <c r="X4">
+        <v>193512353.5229644</v>
+      </c>
+      <c r="Y4">
+        <v>6444334.604952106</v>
+      </c>
+      <c r="Z4">
+        <v>14214.2189624459</v>
+      </c>
+      <c r="AA4">
+        <v>17475.98069615216</v>
+      </c>
+      <c r="AB4">
+        <v>13032.48372695245</v>
+      </c>
+      <c r="AC4">
+        <v>1.229471752357542</v>
+      </c>
+      <c r="AD4">
+        <v>0.981962009152578</v>
+      </c>
+      <c r="AE4">
+        <v>1</v>
+      </c>
+      <c r="AF4">
+        <v>479.7298899825491</v>
+      </c>
+      <c r="AG4">
+        <v>0</v>
+      </c>
+      <c r="AH4">
+        <v>0.009172944960575699</v>
+      </c>
+      <c r="AI4">
+        <v>0.672474724896453</v>
+      </c>
+      <c r="AJ4">
+        <v>0.0156848217397924</v>
+      </c>
+      <c r="AK4">
+        <v>0.0006265703442416</v>
+      </c>
+      <c r="AL4">
+        <v>0.302040938058937</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:40">
+      <c r="A5" t="s">
+        <v>57</v>
+      </c>
+      <c r="B5" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5">
+        <v>166836.0130023361</v>
+      </c>
+      <c r="D5">
+        <v>901.1082482337952</v>
+      </c>
+      <c r="E5">
+        <v>15134</v>
+      </c>
+      <c r="F5">
+        <v>23061</v>
+      </c>
+      <c r="G5">
+        <v>2099</v>
+      </c>
+      <c r="H5">
+        <v>725.3104545708267</v>
+      </c>
+      <c r="I5">
+        <v>-0</v>
+      </c>
+      <c r="J5">
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <v>1627.469491108918</v>
+      </c>
+      <c r="L5">
+        <v>663.3001354279454</v>
+      </c>
+      <c r="M5">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N5">
+        <v>249089.700650978</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <v>89443.15330419608</v>
+      </c>
+      <c r="R5">
+        <v>156865.7378142879</v>
+      </c>
+      <c r="S5">
+        <v>187066310.1842371</v>
+      </c>
+      <c r="T5">
+        <v>6310418.52303097</v>
+      </c>
+      <c r="U5">
+        <v>6993642.88121552</v>
+      </c>
+      <c r="V5">
+        <v>193376728.7072681</v>
+      </c>
+      <c r="W5">
+        <v>194059953.0654526</v>
+      </c>
+      <c r="X5">
+        <v>194037927.0191842</v>
+      </c>
+      <c r="Y5">
+        <v>6805817.114800432</v>
+      </c>
+      <c r="Z5">
+        <v>14333.64846522596</v>
+      </c>
+      <c r="AA5">
+        <v>17657.57469925306</v>
+      </c>
+      <c r="AB5">
+        <v>16530.84253521208</v>
+      </c>
+      <c r="AC5">
+        <v>1.231896731811938</v>
+      </c>
+      <c r="AD5">
+        <v>1</v>
+      </c>
+      <c r="AE5">
+        <v>0.9575061405608248</v>
+      </c>
+      <c r="AF5">
+        <v>520.7275145658982</v>
+      </c>
+      <c r="AG5">
+        <v>57.52373532022232</v>
+      </c>
+      <c r="AH5">
+        <v>0.0384410594950972</v>
+      </c>
+      <c r="AI5">
+        <v>0.6319323627747089</v>
+      </c>
+      <c r="AJ5">
+        <v>0.0228274362678761</v>
+      </c>
+      <c r="AK5">
+        <v>0.0078201055041497</v>
+      </c>
+      <c r="AL5">
+        <v>0.2989790359581681</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:40">
+      <c r="A6" t="s">
+        <v>57</v>
+      </c>
+      <c r="B6" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6">
+        <v>9955.8553160429</v>
+      </c>
+      <c r="D6">
+        <v>719.393440246582</v>
+      </c>
+      <c r="E6">
+        <v>15134</v>
+      </c>
+      <c r="F6">
+        <v>23061</v>
+      </c>
+      <c r="G6">
+        <v>2099</v>
+      </c>
+      <c r="H6">
+        <v>3424.673284532728</v>
+      </c>
+      <c r="I6">
+        <v>-0</v>
+      </c>
+      <c r="J6">
+        <v>-0</v>
+      </c>
+      <c r="K6">
+        <v>2013.85397513202</v>
+      </c>
+      <c r="L6">
+        <v>-0</v>
+      </c>
+      <c r="M6">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N6">
+        <v>1176118.223439116</v>
+      </c>
+      <c r="O6">
+        <v>-0</v>
+      </c>
+      <c r="P6">
+        <v>-0</v>
+      </c>
+      <c r="Q6">
+        <v>110678.234408723</v>
+      </c>
+      <c r="R6">
+        <v>-0</v>
+      </c>
+      <c r="S6">
+        <v>187857708.0503155</v>
+      </c>
+      <c r="T6">
+        <v>4995109.748522402</v>
+      </c>
+      <c r="U6">
+        <v>5265473.67961119</v>
+      </c>
+      <c r="V6">
+        <v>192852817.7988379</v>
+      </c>
+      <c r="W6">
+        <v>193123181.7299267</v>
+      </c>
+      <c r="X6">
+        <v>193123128.106603</v>
+      </c>
+      <c r="Y6">
+        <v>6281906.206370241</v>
+      </c>
+      <c r="Z6">
+        <v>14241.54442174163</v>
+      </c>
+      <c r="AA6">
+        <v>17509.07136892886</v>
+      </c>
+      <c r="AB6">
+        <v>12439.77337700343</v>
+      </c>
+      <c r="AC6">
+        <v>1.229436278146836</v>
+      </c>
+      <c r="AD6">
+        <v>0.9528661976551128</v>
+      </c>
+      <c r="AE6">
+        <v>1</v>
+      </c>
+      <c r="AF6">
+        <v>480.65212423378</v>
+      </c>
+      <c r="AG6">
+        <v>0</v>
+      </c>
+      <c r="AH6">
+        <v>0.0171536911308068</v>
+      </c>
+      <c r="AI6">
+        <v>0.6593603673884244</v>
+      </c>
+      <c r="AJ6">
+        <v>0.0157404492582387</v>
+      </c>
+      <c r="AK6">
+        <v>0.009205679401609299</v>
+      </c>
+      <c r="AL6">
+        <v>0.2985398128209207</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN6">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:40">
+      <c r="A7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7">
+        <v>9999.717520177364</v>
+      </c>
+      <c r="D7">
+        <v>418.7610490322113</v>
+      </c>
+      <c r="E7">
+        <v>15066</v>
+      </c>
+      <c r="F7">
+        <v>23041</v>
+      </c>
+      <c r="G7">
+        <v>2099</v>
+      </c>
+      <c r="H7">
+        <v>3341.156928133621</v>
+      </c>
+      <c r="I7">
+        <v>-0</v>
+      </c>
+      <c r="J7">
+        <v>-0</v>
+      </c>
+      <c r="K7">
+        <v>1938.776933843432</v>
+      </c>
+      <c r="L7">
+        <v>25.9546513998975</v>
+      </c>
+      <c r="M7">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N7">
+        <v>1147436.623603052</v>
+      </c>
+      <c r="O7">
+        <v>-0</v>
+      </c>
+      <c r="P7">
+        <v>-0</v>
+      </c>
+      <c r="Q7">
+        <v>106552.1187732004</v>
+      </c>
+      <c r="R7">
+        <v>6138.089416988876</v>
+      </c>
+      <c r="S7">
+        <v>187831038.4242609</v>
+      </c>
+      <c r="T7">
+        <v>5023395.814163911</v>
+      </c>
+      <c r="U7">
+        <v>5296094.454266522</v>
+      </c>
+      <c r="V7">
+        <v>192854434.2384248</v>
+      </c>
+      <c r="W7">
+        <v>193127132.8785274</v>
+      </c>
+      <c r="X7">
+        <v>192854434.2384248</v>
+      </c>
+      <c r="Y7">
+        <v>6283522.645957153</v>
+      </c>
+      <c r="Z7">
+        <v>14212.83858441838</v>
+      </c>
+      <c r="AA7">
+        <v>17474.87659323662</v>
+      </c>
+      <c r="AB7">
+        <v>12523.08654784168</v>
+      </c>
+      <c r="AC7">
+        <v>1.229513477511411</v>
+      </c>
+      <c r="AD7">
+        <v>0.9540444153736102</v>
+      </c>
+      <c r="AE7">
+        <v>0.9993345081230006</v>
+      </c>
+      <c r="AF7">
+        <v>480.2508139417424</v>
+      </c>
+      <c r="AG7">
+        <v>0.886737058784402</v>
+      </c>
+      <c r="AH7">
+        <v>0.0073466594370467</v>
+      </c>
+      <c r="AI7">
+        <v>0.6745217787724095</v>
+      </c>
+      <c r="AJ7">
+        <v>0.0155855350558397</v>
+      </c>
+      <c r="AK7">
+        <v>0.0015709542120487</v>
+      </c>
+      <c r="AL7">
+        <v>0.3009750725226552</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:40">
+      <c r="A8" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8">
+        <v>7716.731516122818</v>
+      </c>
+      <c r="D8">
+        <v>480.4685471057892</v>
+      </c>
+      <c r="E8">
+        <v>15134</v>
+      </c>
+      <c r="F8">
+        <v>23061</v>
+      </c>
+      <c r="G8">
+        <v>2099</v>
+      </c>
+      <c r="H8">
+        <v>0</v>
+      </c>
+      <c r="I8">
+        <v>1636.340526861083</v>
+      </c>
+      <c r="J8">
+        <v>4976.705187956389</v>
+      </c>
+      <c r="K8">
+        <v>1964.571357598373</v>
+      </c>
+      <c r="L8">
+        <v>-0</v>
+      </c>
+      <c r="M8">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N8">
+        <v>0</v>
+      </c>
+      <c r="O8">
+        <v>21029.02110249023</v>
+      </c>
+      <c r="P8">
+        <v>601206.3217949715</v>
+      </c>
+      <c r="Q8">
+        <v>107969.7395709546</v>
+      </c>
+      <c r="R8">
+        <v>-0</v>
+      </c>
+      <c r="S8">
+        <v>187301116.6749361</v>
+      </c>
+      <c r="T8">
+        <v>5696786.005459454</v>
+      </c>
+      <c r="U8">
+        <v>5894692.705885455</v>
+      </c>
+      <c r="V8">
+        <v>192997902.6803956</v>
+      </c>
+      <c r="W8">
+        <v>193195809.3808216</v>
+      </c>
+      <c r="X8">
+        <v>193193572.4625033</v>
+      </c>
+      <c r="Y8">
+        <v>6426991.08792787</v>
+      </c>
+      <c r="Z8">
+        <v>14216.24476001392</v>
+      </c>
+      <c r="AA8">
+        <v>17478.43390302088</v>
+      </c>
+      <c r="AB8">
+        <v>17921.1844439866</v>
+      </c>
+      <c r="AC8">
+        <v>1.229469117764666</v>
+      </c>
+      <c r="AD8">
+        <v>0</v>
+      </c>
+      <c r="AE8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>479.7982606504698</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8">
+        <v>0.0159881366914172</v>
+      </c>
+      <c r="AI8">
+        <v>0.6657123789800237</v>
+      </c>
+      <c r="AJ8">
+        <v>0.015587461651985</v>
+      </c>
+      <c r="AK8">
+        <v>2.689712794530913E-18</v>
+      </c>
+      <c r="AL8">
+        <v>0.302712022676574</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN8">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:40">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+      <c r="B9" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9">
+        <v>9110.868020325899</v>
+      </c>
+      <c r="D9">
+        <v>210.1079816818237</v>
+      </c>
+      <c r="E9">
+        <v>15066</v>
+      </c>
+      <c r="F9">
+        <v>23041</v>
+      </c>
+      <c r="G9">
+        <v>2099</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1652.009165007447</v>
+      </c>
+      <c r="J9">
+        <v>4983.079812167604</v>
+      </c>
+      <c r="K9">
+        <v>1930.426268505076</v>
+      </c>
+      <c r="L9">
+        <v>-0</v>
+      </c>
+      <c r="M9">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N9">
+        <v>0</v>
+      </c>
+      <c r="O9">
+        <v>21230.38268757498</v>
+      </c>
+      <c r="P9">
+        <v>601976.4024467499</v>
+      </c>
+      <c r="Q9">
+        <v>106093.179392689</v>
+      </c>
+      <c r="R9">
+        <v>-0</v>
+      </c>
+      <c r="S9">
+        <v>187300211.5569947</v>
+      </c>
+      <c r="T9">
+        <v>5695302.353442986</v>
+      </c>
+      <c r="U9">
+        <v>5892209.303503102</v>
+      </c>
+      <c r="V9">
+        <v>192995513.9104377</v>
+      </c>
+      <c r="W9">
+        <v>193192420.8604978</v>
+      </c>
+      <c r="X9">
+        <v>192995513.9104377</v>
+      </c>
+      <c r="Y9">
+        <v>6424602.31797</v>
+      </c>
+      <c r="Z9">
+        <v>14215.6867325082</v>
+      </c>
+      <c r="AA9">
+        <v>17477.7581410733</v>
+      </c>
+      <c r="AB9">
+        <v>17921.10654474974</v>
+      </c>
+      <c r="AC9">
+        <v>1.22946984341639</v>
+      </c>
+      <c r="AD9">
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <v>1</v>
+      </c>
+      <c r="AF9">
+        <v>479.7794272221518</v>
+      </c>
+      <c r="AG9">
+        <v>-1.105884340828817E-15</v>
+      </c>
+      <c r="AH9">
+        <v>0.0147283656277901</v>
+      </c>
+      <c r="AI9">
+        <v>0.6669932367459059</v>
+      </c>
+      <c r="AJ9">
+        <v>0.0155864290139226</v>
+      </c>
+      <c r="AK9">
+        <v>0</v>
+      </c>
+      <c r="AL9">
+        <v>0.3026919686123813</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>89</v>
+      </c>
+      <c r="AN9">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:40">
+      <c r="A10" t="s">
+        <v>57</v>
+      </c>
+      <c r="B10" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10">
+        <v>59362.84984251857</v>
+      </c>
+      <c r="D10">
+        <v>900.9801826477052</v>
+      </c>
+      <c r="E10">
+        <v>15134</v>
+      </c>
+      <c r="F10">
+        <v>21141</v>
+      </c>
+      <c r="G10">
+        <v>2099</v>
+      </c>
+      <c r="H10">
+        <v>2968.605923617521</v>
+      </c>
+      <c r="I10">
+        <v>-0</v>
+      </c>
+      <c r="J10">
+        <v>-0</v>
+      </c>
+      <c r="K10">
+        <v>1941.218693547999</v>
+      </c>
+      <c r="L10">
+        <v>-0</v>
+      </c>
+      <c r="M10">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N10">
+        <v>1019493.316558007</v>
+      </c>
+      <c r="O10">
+        <v>-0</v>
+      </c>
+      <c r="P10">
+        <v>-0</v>
+      </c>
+      <c r="Q10">
+        <v>106686.3140307955</v>
+      </c>
+      <c r="R10">
+        <v>-0</v>
+      </c>
+      <c r="S10">
+        <v>187697091.2230565</v>
+      </c>
+      <c r="T10">
+        <v>5315719.228897353</v>
+      </c>
+      <c r="U10">
+        <v>5573838.81687875</v>
+      </c>
+      <c r="V10">
+        <v>193012810.4519538</v>
+      </c>
+      <c r="W10">
+        <v>193270930.0399352</v>
+      </c>
+      <c r="X10">
+        <v>193266644.0093575</v>
+      </c>
+      <c r="Y10">
+        <v>6441898.859486155</v>
+      </c>
+      <c r="Z10">
+        <v>14218.22750032873</v>
+      </c>
+      <c r="AA10">
+        <v>17480.83496827832</v>
+      </c>
+      <c r="AB10">
+        <v>12961.47501870416</v>
+      </c>
+      <c r="AC10">
+        <v>1.229466539895648</v>
+      </c>
+      <c r="AD10">
+        <v>0.9800035034498688</v>
+      </c>
+      <c r="AE10">
+        <v>1</v>
+      </c>
+      <c r="AF10">
+        <v>479.8651781360946</v>
+      </c>
+      <c r="AG10">
+        <v>0</v>
+      </c>
+      <c r="AH10">
+        <v>0.0135830758806656</v>
+      </c>
+      <c r="AI10">
+        <v>0.6674935110412664</v>
+      </c>
+      <c r="AJ10">
+        <v>0.0156161001659087</v>
+      </c>
+      <c r="AK10">
+        <v>0.0007990124484323</v>
+      </c>
+      <c r="AL10">
+        <v>0.3025083004637269</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN10">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="11" spans="1:40">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11">
+        <v>25321.86885163188</v>
+      </c>
+      <c r="D11">
+        <v>900.19162774086</v>
+      </c>
+      <c r="E11">
+        <v>15066</v>
+      </c>
+      <c r="F11">
+        <v>21121</v>
+      </c>
+      <c r="G11">
+        <v>2099</v>
+      </c>
+      <c r="H11">
+        <v>3088.397125915816</v>
+      </c>
+      <c r="I11">
+        <v>-0</v>
+      </c>
+      <c r="J11">
+        <v>-0</v>
+      </c>
+      <c r="K11">
+        <v>1894.95256675468</v>
+      </c>
+      <c r="L11">
+        <v>-0</v>
+      </c>
+      <c r="M11">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N11">
+        <v>1060632.603235957</v>
+      </c>
+      <c r="O11">
+        <v>-0</v>
+      </c>
+      <c r="P11">
+        <v>-0</v>
+      </c>
+      <c r="Q11">
+        <v>104143.6007607934</v>
+      </c>
+      <c r="R11">
+        <v>-0</v>
+      </c>
+      <c r="S11">
+        <v>187735687.7964644</v>
+      </c>
+      <c r="T11">
+        <v>5272283.701197506</v>
+      </c>
+      <c r="U11">
+        <v>5529038.904650423</v>
+      </c>
+      <c r="V11">
+        <v>193007971.4976619</v>
+      </c>
+      <c r="W11">
+        <v>193264726.7011148</v>
+      </c>
+      <c r="X11">
+        <v>193007971.4976619</v>
+      </c>
+      <c r="Y11">
+        <v>6437059.905194256</v>
+      </c>
+      <c r="Z11">
+        <v>14213.49709012488</v>
+      </c>
+      <c r="AA11">
+        <v>17475.10652088203</v>
+      </c>
+      <c r="AB11">
+        <v>12813.32572681972</v>
+      </c>
+      <c r="AC11">
+        <v>1.229472691349352</v>
+      </c>
+      <c r="AD11">
+        <v>0.9716770696990298</v>
+      </c>
+      <c r="AE11">
+        <v>1</v>
+      </c>
+      <c r="AF11">
+        <v>479.7055267917148</v>
+      </c>
+      <c r="AG11">
+        <v>0</v>
+      </c>
+      <c r="AH11">
+        <v>0.008894227682659401</v>
+      </c>
+      <c r="AI11">
+        <v>0.6729519980216252</v>
+      </c>
+      <c r="AJ11">
+        <v>0.0160365488208178</v>
+      </c>
+      <c r="AK11">
+        <v>0.0002488456648426</v>
+      </c>
+      <c r="AL11">
+        <v>0.3018683798100549</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN11">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:40">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>60</v>
+      </c>
+      <c r="C12">
+        <v>9946.960632830858</v>
+      </c>
+      <c r="D12">
+        <v>836.8702623844147</v>
+      </c>
+      <c r="E12">
+        <v>15134</v>
+      </c>
+      <c r="F12">
+        <v>23061</v>
+      </c>
+      <c r="G12">
+        <v>2099</v>
+      </c>
+      <c r="H12">
+        <v>3068.275742290277</v>
+      </c>
+      <c r="I12">
+        <v>-0</v>
+      </c>
+      <c r="J12">
+        <v>-0</v>
+      </c>
+      <c r="K12">
+        <v>1523.130823721258</v>
+      </c>
+      <c r="L12">
+        <v>-0</v>
+      </c>
+      <c r="M12">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N12">
+        <v>1053722.418235335</v>
+      </c>
+      <c r="O12">
+        <v>-0</v>
+      </c>
+      <c r="P12">
+        <v>-0</v>
+      </c>
+      <c r="Q12">
+        <v>83708.86490512373</v>
+      </c>
+      <c r="R12">
+        <v>-0</v>
+      </c>
+      <c r="S12">
+        <v>187708342.8756081</v>
+      </c>
+      <c r="T12">
+        <v>5495244.349183235</v>
+      </c>
+      <c r="U12">
+        <v>5759254.215358049</v>
+      </c>
+      <c r="V12">
+        <v>193203587.2247913</v>
+      </c>
+      <c r="W12">
+        <v>193467597.0909662</v>
+      </c>
+      <c r="X12">
+        <v>193465852.0233703</v>
+      </c>
+      <c r="Y12">
+        <v>6632675.632323695</v>
+      </c>
+      <c r="Z12">
+        <v>14214.28104434482</v>
+      </c>
+      <c r="AA12">
+        <v>18064.06815756718</v>
+      </c>
+      <c r="AB12">
+        <v>13398.89320758878</v>
+      </c>
+      <c r="AC12">
+        <v>1.270839383378733</v>
+      </c>
+      <c r="AD12">
+        <v>0.978761310607775</v>
+      </c>
+      <c r="AE12">
+        <v>1</v>
+      </c>
+      <c r="AF12">
+        <v>383.7855881973101</v>
+      </c>
+      <c r="AG12">
+        <v>0</v>
+      </c>
+      <c r="AH12">
+        <v>0.0104402883323688</v>
+      </c>
+      <c r="AI12">
+        <v>0.6712831165331651</v>
+      </c>
+      <c r="AJ12">
+        <v>0.0156228224430471</v>
+      </c>
+      <c r="AK12">
+        <v>0.0005089996861793</v>
+      </c>
+      <c r="AL12">
+        <v>0.3021447730052397</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN12">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:40">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13">
+        <v>3832.937383204699</v>
+      </c>
+      <c r="D13">
+        <v>713.8842849731445</v>
+      </c>
+      <c r="E13">
+        <v>15134</v>
+      </c>
+      <c r="F13">
+        <v>23061</v>
+      </c>
+      <c r="G13">
+        <v>2099</v>
+      </c>
+      <c r="H13">
+        <v>2935.382650726602</v>
+      </c>
+      <c r="I13">
+        <v>-0</v>
+      </c>
+      <c r="J13">
+        <v>-0</v>
+      </c>
+      <c r="K13">
+        <v>2066.191416766348</v>
+      </c>
+      <c r="L13">
+        <v>-0</v>
+      </c>
+      <c r="M13">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N13">
+        <v>1008083.615998898</v>
+      </c>
+      <c r="O13">
+        <v>-0</v>
+      </c>
+      <c r="P13">
+        <v>-0</v>
+      </c>
+      <c r="Q13">
+        <v>113554.6175552107</v>
+      </c>
+      <c r="R13">
+        <v>-0</v>
+      </c>
+      <c r="S13">
+        <v>187692549.8260218</v>
+      </c>
+      <c r="T13">
+        <v>5255077.644518276</v>
+      </c>
+      <c r="U13">
+        <v>5510802.366946987</v>
+      </c>
+      <c r="V13">
+        <v>192947627.47054</v>
+      </c>
+      <c r="W13">
+        <v>193203352.1929688</v>
+      </c>
+      <c r="X13">
+        <v>193199623.4609974</v>
+      </c>
+      <c r="Y13">
+        <v>6376715.878072385</v>
+      </c>
+      <c r="Z13">
+        <v>14215.58030258137</v>
+      </c>
+      <c r="AA13">
+        <v>17281.60724667837</v>
+      </c>
+      <c r="AB13">
+        <v>12816.82005589555</v>
+      </c>
+      <c r="AC13">
+        <v>1.215680744565894</v>
+      </c>
+      <c r="AD13">
+        <v>0.9791275844501004</v>
+      </c>
+      <c r="AE13">
+        <v>1</v>
+      </c>
+      <c r="AF13">
+        <v>511.7608908929293</v>
+      </c>
+      <c r="AG13">
+        <v>0</v>
+      </c>
+      <c r="AH13">
+        <v>0.0104367457982305</v>
+      </c>
+      <c r="AI13">
+        <v>0.6710553408931553</v>
+      </c>
+      <c r="AJ13">
+        <v>0.0157285687225698</v>
+      </c>
+      <c r="AK13">
+        <v>0.0012468120160625</v>
+      </c>
+      <c r="AL13">
+        <v>0.3015325325699818</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>91</v>
+      </c>
+      <c r="AN13">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:40">
+      <c r="A14" t="s">
+        <v>57</v>
+      </c>
+      <c r="B14" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14">
+        <v>9762.70738774538</v>
+      </c>
+      <c r="D14">
+        <v>178.7758738994598</v>
+      </c>
+      <c r="E14">
+        <v>15134</v>
+      </c>
+      <c r="F14">
+        <v>23061</v>
+      </c>
+      <c r="G14">
+        <v>2099</v>
+      </c>
+      <c r="H14">
+        <v>2968.60592361752</v>
+      </c>
+      <c r="I14">
+        <v>-0</v>
+      </c>
+      <c r="J14">
+        <v>-0</v>
+      </c>
+      <c r="K14">
+        <v>2010.976915932183</v>
+      </c>
+      <c r="L14">
+        <v>-0</v>
+      </c>
+      <c r="M14">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N14">
+        <v>1019493.316558007</v>
+      </c>
+      <c r="O14">
+        <v>-0</v>
+      </c>
+      <c r="P14">
+        <v>-0</v>
+      </c>
+      <c r="Q14">
+        <v>110520.1157782466</v>
+      </c>
+      <c r="R14">
+        <v>-0</v>
+      </c>
+      <c r="S14">
+        <v>187700925.0248039</v>
+      </c>
+      <c r="T14">
+        <v>5317401.46693185</v>
+      </c>
+      <c r="U14">
+        <v>5573090.46464166</v>
+      </c>
+      <c r="V14">
+        <v>193018326.4917358</v>
+      </c>
+      <c r="W14">
+        <v>193274015.4894456</v>
+      </c>
+      <c r="X14">
+        <v>193274302.1083991</v>
+      </c>
+      <c r="Y14">
+        <v>6447414.899268104</v>
+      </c>
+      <c r="Z14">
+        <v>14216.92966784751</v>
+      </c>
+      <c r="AA14">
+        <v>17479.26331491688</v>
+      </c>
+      <c r="AB14">
+        <v>12965.11460079566</v>
+      </c>
+      <c r="AC14">
+        <v>1.229468227197279</v>
+      </c>
+      <c r="AD14">
+        <v>0.978873469759666</v>
+      </c>
+      <c r="AE14">
+        <v>1</v>
+      </c>
+      <c r="AF14">
+        <v>479.8213762898536</v>
+      </c>
+      <c r="AG14">
+        <v>0</v>
+      </c>
+      <c r="AH14">
+        <v>0.0138958324482066</v>
+      </c>
+      <c r="AI14">
+        <v>0.667546777358683</v>
+      </c>
+      <c r="AJ14">
+        <v>0.0156901257866627</v>
+      </c>
+      <c r="AK14">
+        <v>0.0009108351348459</v>
+      </c>
+      <c r="AL14">
+        <v>0.3019564292716017</v>
+      </c>
+      <c r="AM14" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:40">
+      <c r="A15" t="s">
+        <v>57</v>
+      </c>
+      <c r="B15" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15">
+        <v>99751.18298575282</v>
+      </c>
+      <c r="D15">
+        <v>901.2040162086488</v>
+      </c>
+      <c r="E15">
+        <v>15134</v>
+      </c>
+      <c r="F15">
+        <v>23061</v>
+      </c>
+      <c r="G15">
+        <v>2099</v>
+      </c>
+      <c r="H15">
+        <v>2980.061046588183</v>
+      </c>
+      <c r="I15">
+        <v>-0</v>
+      </c>
+      <c r="J15">
+        <v>-0</v>
+      </c>
+      <c r="K15">
+        <v>2591.685575318846</v>
+      </c>
+      <c r="L15">
+        <v>-0</v>
+      </c>
+      <c r="M15">
+        <v>186570911.5924677</v>
+      </c>
+      <c r="N15">
+        <v>1023427.291497567</v>
+      </c>
+      <c r="O15">
+        <v>-0</v>
+      </c>
+      <c r="P15">
+        <v>-0</v>
+      </c>
+      <c r="Q15">
+        <v>142434.9467046344</v>
+      </c>
+      <c r="R15">
+        <v>-0</v>
+      </c>
+      <c r="S15">
+        <v>187736773.8306699</v>
+      </c>
+      <c r="T15">
+        <v>5306862.797506566</v>
+      </c>
+      <c r="U15">
+        <v>5559177.886820337</v>
+      </c>
+      <c r="V15">
+        <v>193043636.6281765</v>
+      </c>
+      <c r="W15">
+        <v>193295951.7174902</v>
+      </c>
+      <c r="X15">
+        <v>193292060.6555821</v>
+      </c>
+      <c r="Y15">
+        <v>6472725.035708768</v>
+      </c>
+      <c r="Z15">
+        <v>14235.13069132942</v>
+      </c>
+      <c r="AA15">
+        <v>17501.30444900076</v>
+      </c>
+      <c r="AB15">
+        <v>12951.94794567519</v>
+      </c>
+      <c r="AC15">
+        <v>1.229444592290309</v>
+      </c>
+      <c r="AD15">
+        <v>0.9827160648291172</v>
+      </c>
+      <c r="AE15">
+        <v>1</v>
+      </c>
+      <c r="AF15">
+        <v>480.435660832368</v>
+      </c>
+      <c r="AG15">
+        <v>0</v>
+      </c>
+      <c r="AH15">
+        <v>0.0108514096425054</v>
+      </c>
+      <c r="AI15">
+        <v>0.6677085111705873</v>
+      </c>
+      <c r="AJ15">
+        <v>0.0157404138591512</v>
+      </c>
+      <c r="AK15">
+        <v>0.0048478273916892</v>
+      </c>
+      <c r="AL15">
+        <v>0.3008518379360668</v>
+      </c>
+      <c r="AM15" t="s">
+        <v>92</v>
+      </c>
+      <c r="AN15">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:40">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C16">
+        <v>86757.14096429944</v>
+      </c>
+      <c r="D16">
+        <v>901.207781791687</v>
+      </c>
+      <c r="E16">
+        <v>15134</v>
+      </c>
+      <c r="F16">
+        <v>24021</v>
+      </c>
+      <c r="G16">
+        <v>2106</v>
+      </c>
+      <c r="H16">
+        <v>2984.395885227936</v>
+      </c>
+      <c r="I16">
+        <v>-0</v>
+      </c>
+      <c r="J16">
+        <v>-0</v>
+      </c>
+      <c r="K16">
+        <v>1571.36766901559</v>
+      </c>
+      <c r="L16">
+        <v>1218.068163432576</v>
+      </c>
+      <c r="M16">
+        <v>187193110.9165016</v>
+      </c>
+      <c r="N16">
+        <v>1024915.983205155</v>
+      </c>
+      <c r="O16">
+        <v>-0</v>
+      </c>
+      <c r="P16">
+        <v>-0</v>
+      </c>
+      <c r="Q16">
+        <v>86359.88575199194</v>
+      </c>
+      <c r="R16">
+        <v>288064.4084923482</v>
+      </c>
+      <c r="S16">
+        <v>188592451.1939511</v>
+      </c>
+      <c r="T16">
+        <v>5337853.42471143</v>
+      </c>
+      <c r="U16">
+        <v>5593000.577675563</v>
+      </c>
+      <c r="V16">
+        <v>193930304.6186625</v>
+      </c>
+      <c r="W16">
+        <v>194185451.7716267</v>
+      </c>
+      <c r="X16">
+        <v>194184335.2573225</v>
+      </c>
+      <c r="Y16">
+        <v>6737193.702160925</v>
+      </c>
+      <c r="Z16">
+        <v>14250.58787553514</v>
+      </c>
+      <c r="AA16">
+        <v>17560.75808289598</v>
+      </c>
+      <c r="AB16">
+        <v>13022.32837678368</v>
+      </c>
+      <c r="AC16">
+        <v>1.232283063426711</v>
+      </c>
+      <c r="AD16">
+        <v>0.9789317764791224</v>
+      </c>
+      <c r="AE16">
+        <v>0.9525310430233376</v>
+      </c>
+      <c r="AF16">
+        <v>521.6925839416093</v>
+      </c>
+      <c r="AG16">
+        <v>63.56578646031115</v>
+      </c>
+      <c r="AH16">
+        <v>0.0104680083118247</v>
+      </c>
+      <c r="AI16">
+        <v>0.671285548724306</v>
+      </c>
+      <c r="AJ16">
+        <v>0.0142310220236448</v>
+      </c>
+      <c r="AK16">
+        <v>0.0020449705896447</v>
+      </c>
+      <c r="AL16">
+        <v>0.3019704503505797</v>
+      </c>
+      <c r="AM16" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN16">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:40">
+      <c r="A17" t="s">
+        <v>56</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17">
+        <v>115227.5618632734</v>
+      </c>
+      <c r="D17">
+        <v>900.5524597167969</v>
+      </c>
+      <c r="E17">
+        <v>15066</v>
+      </c>
+      <c r="F17">
+        <v>24001</v>
+      </c>
+      <c r="G17">
+        <v>2106</v>
+      </c>
+      <c r="H17">
+        <v>2996.219261914863</v>
+      </c>
+      <c r="I17">
+        <v>-6.31014964209069E-13</v>
+      </c>
+      <c r="J17">
+        <v>-1.262029928418138E-12</v>
+      </c>
+      <c r="K17">
+        <v>1356.081032807438</v>
+      </c>
+      <c r="L17">
+        <v>1200.501786975759</v>
+      </c>
+      <c r="M17">
+        <v>187193110.9165016</v>
+      </c>
+      <c r="N17">
+        <v>1028976.425655792</v>
+      </c>
+      <c r="O17">
+        <v>-8.109331022800091E-12</v>
+      </c>
+      <c r="P17">
+        <v>-1.524583720762864E-10</v>
+      </c>
+      <c r="Q17">
+        <v>74528.07218380645</v>
+      </c>
+      <c r="R17">
+        <v>283910.0861027648</v>
+      </c>
+      <c r="S17">
+        <v>188580525.500444</v>
+      </c>
+      <c r="T17">
+        <v>5343119.564116536</v>
+      </c>
+      <c r="U17">
+        <v>5598974.643401673</v>
+      </c>
+      <c r="V17">
+        <v>193923645.0645605</v>
+      </c>
+      <c r="W17">
+        <v>194179500.1438456</v>
+      </c>
+      <c r="X17">
+        <v>193923645.0645605</v>
+      </c>
+      <c r="Y17">
+        <v>6730534.148058899</v>
+      </c>
+      <c r="Z17">
+        <v>14249.0589467486</v>
+      </c>
+      <c r="AA17">
+        <v>17589.11488168997</v>
+      </c>
+      <c r="AB17">
+        <v>13038.20684539529</v>
+      </c>
+      <c r="AC17">
+        <v>1.234405370026455</v>
+      </c>
+      <c r="AD17">
+        <v>0.977749749175907</v>
+      </c>
+      <c r="AE17">
+        <v>0.9229152233769354</v>
+      </c>
+      <c r="AF17">
+        <v>551.8492884992046</v>
+      </c>
+      <c r="AG17">
+        <v>108.0140605489054</v>
+      </c>
+      <c r="AH17">
+        <v>0.0073042202722968</v>
+      </c>
+      <c r="AI17">
+        <v>0.6744953606932355</v>
+      </c>
+      <c r="AJ17">
+        <v>0.0142285089032656</v>
+      </c>
+      <c r="AK17">
+        <v>0.0015713954358942</v>
+      </c>
+      <c r="AL17">
+        <v>0.3024005146953076</v>
+      </c>
+      <c r="AM17" t="s">
+        <v>90</v>
+      </c>
+      <c r="AN17">
+        <v>1.1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:I47"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>78</v>
+      </c>
+      <c r="B1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s">
+        <v>87</v>
+      </c>
+      <c r="D1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F1" t="s">
+        <v>96</v>
+      </c>
+      <c r="G1" t="s">
+        <v>97</v>
+      </c>
+      <c r="H1" t="s">
+        <v>98</v>
+      </c>
+      <c r="I1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>100</v>
+      </c>
+      <c r="B2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2" t="s">
+        <v>156</v>
+      </c>
+      <c r="D2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F2" t="s">
+        <v>261</v>
+      </c>
+      <c r="G2" t="s">
+        <v>273</v>
+      </c>
+      <c r="H2" t="s">
+        <v>311</v>
+      </c>
+      <c r="I2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C3" t="s">
+        <v>157</v>
+      </c>
+      <c r="D3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E3" t="s">
+        <v>240</v>
+      </c>
+      <c r="F3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G3" t="s">
+        <v>262</v>
+      </c>
+      <c r="H3" t="s">
+        <v>312</v>
+      </c>
+      <c r="I3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E4" t="s">
+        <v>241</v>
+      </c>
+      <c r="F4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G4" t="s">
+        <v>274</v>
+      </c>
+      <c r="H4" t="s">
+        <v>313</v>
+      </c>
+      <c r="I4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>100</v>
+      </c>
+      <c r="B5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C5" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" t="s">
+        <v>204</v>
+      </c>
+      <c r="E5" t="s">
+        <v>242</v>
+      </c>
+      <c r="F5" t="s">
+        <v>209</v>
+      </c>
+      <c r="G5" t="s">
+        <v>275</v>
+      </c>
+      <c r="H5" t="s">
+        <v>314</v>
+      </c>
+      <c r="I5" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>101</v>
+      </c>
+      <c r="B6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" t="s">
+        <v>160</v>
+      </c>
+      <c r="D6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E6" t="s">
+        <v>243</v>
+      </c>
+      <c r="F6" t="s">
+        <v>264</v>
+      </c>
+      <c r="G6" t="s">
+        <v>276</v>
+      </c>
+      <c r="H6" t="s">
+        <v>315</v>
+      </c>
+      <c r="I6" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" t="s">
+        <v>206</v>
+      </c>
+      <c r="E7" t="s">
+        <v>243</v>
+      </c>
+      <c r="F7" t="s">
+        <v>265</v>
+      </c>
+      <c r="G7" t="s">
+        <v>277</v>
+      </c>
+      <c r="H7" t="s">
+        <v>316</v>
+      </c>
+      <c r="I7" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>101</v>
+      </c>
+      <c r="B8" t="s">
+        <v>116</v>
+      </c>
+      <c r="C8" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" t="s">
+        <v>207</v>
+      </c>
+      <c r="E8" t="s">
+        <v>209</v>
+      </c>
+      <c r="F8" t="s">
+        <v>266</v>
+      </c>
+      <c r="G8" t="s">
+        <v>278</v>
+      </c>
+      <c r="H8" t="s">
+        <v>314</v>
+      </c>
+      <c r="I8" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>101</v>
+      </c>
+      <c r="B9" t="s">
+        <v>117</v>
+      </c>
+      <c r="C9" t="s">
+        <v>163</v>
+      </c>
+      <c r="D9" t="s">
+        <v>208</v>
+      </c>
+      <c r="E9" t="s">
+        <v>209</v>
+      </c>
+      <c r="F9" t="s">
+        <v>266</v>
+      </c>
+      <c r="G9" t="s">
+        <v>279</v>
+      </c>
+      <c r="H9" t="s">
+        <v>314</v>
+      </c>
+      <c r="I9" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>102</v>
+      </c>
+      <c r="B10" t="s">
+        <v>118</v>
+      </c>
+      <c r="C10" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" t="s">
+        <v>209</v>
+      </c>
+      <c r="E10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F10" t="s">
+        <v>264</v>
+      </c>
+      <c r="G10" t="s">
+        <v>280</v>
+      </c>
+      <c r="H10" t="s">
+        <v>314</v>
+      </c>
+      <c r="I10" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" t="s">
+        <v>165</v>
+      </c>
+      <c r="D11" t="s">
+        <v>210</v>
+      </c>
+      <c r="E11" t="s">
+        <v>245</v>
+      </c>
+      <c r="F11" t="s">
+        <v>264</v>
+      </c>
+      <c r="G11" t="s">
+        <v>281</v>
+      </c>
+      <c r="H11" t="s">
+        <v>317</v>
+      </c>
+      <c r="I11" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B12" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" t="s">
+        <v>166</v>
+      </c>
+      <c r="D12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" t="s">
+        <v>244</v>
+      </c>
+      <c r="F12" t="s">
+        <v>264</v>
+      </c>
+      <c r="G12" t="s">
+        <v>282</v>
+      </c>
+      <c r="H12" t="s">
+        <v>314</v>
+      </c>
+      <c r="I12" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B13" t="s">
+        <v>121</v>
+      </c>
+      <c r="C13" t="s">
+        <v>167</v>
+      </c>
+      <c r="D13" t="s">
+        <v>211</v>
+      </c>
+      <c r="E13" t="s">
+        <v>246</v>
+      </c>
+      <c r="F13" t="s">
+        <v>264</v>
+      </c>
+      <c r="G13" t="s">
+        <v>283</v>
+      </c>
+      <c r="H13" t="s">
+        <v>318</v>
+      </c>
+      <c r="I13" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>102</v>
+      </c>
+      <c r="B14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" t="s">
+        <v>168</v>
+      </c>
+      <c r="D14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E14" t="s">
+        <v>246</v>
+      </c>
+      <c r="F14" t="s">
+        <v>264</v>
+      </c>
+      <c r="G14" t="s">
+        <v>284</v>
+      </c>
+      <c r="H14" t="s">
+        <v>312</v>
+      </c>
+      <c r="I14" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" t="s">
+        <v>169</v>
+      </c>
+      <c r="D15" t="s">
+        <v>213</v>
+      </c>
+      <c r="E15" t="s">
+        <v>209</v>
+      </c>
+      <c r="F15" t="s">
+        <v>264</v>
+      </c>
+      <c r="G15" t="s">
+        <v>285</v>
+      </c>
+      <c r="H15" t="s">
+        <v>315</v>
+      </c>
+      <c r="I15" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>103</v>
+      </c>
+      <c r="B16" t="s">
+        <v>124</v>
+      </c>
+      <c r="C16" t="s">
+        <v>170</v>
+      </c>
+      <c r="D16" t="s">
+        <v>214</v>
+      </c>
+      <c r="E16" t="s">
+        <v>241</v>
+      </c>
+      <c r="F16" t="s">
+        <v>264</v>
+      </c>
+      <c r="G16" t="s">
+        <v>286</v>
+      </c>
+      <c r="H16" t="s">
+        <v>315</v>
+      </c>
+      <c r="I16" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>103</v>
+      </c>
+      <c r="B17" t="s">
+        <v>125</v>
+      </c>
+      <c r="C17" t="s">
+        <v>171</v>
+      </c>
+      <c r="D17" t="s">
+        <v>215</v>
+      </c>
+      <c r="E17" t="s">
+        <v>247</v>
+      </c>
+      <c r="F17" t="s">
+        <v>264</v>
+      </c>
+      <c r="G17" t="s">
+        <v>287</v>
+      </c>
+      <c r="H17" t="s">
+        <v>317</v>
+      </c>
+      <c r="I17" t="s">
+        <v>329</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>103</v>
+      </c>
+      <c r="B18" t="s">
+        <v>126</v>
+      </c>
+      <c r="C18" t="s">
+        <v>172</v>
+      </c>
+      <c r="D18" t="s">
+        <v>216</v>
+      </c>
+      <c r="E18" t="s">
+        <v>241</v>
+      </c>
+      <c r="F18" t="s">
+        <v>267</v>
+      </c>
+      <c r="G18" t="s">
+        <v>288</v>
+      </c>
+      <c r="H18" t="s">
+        <v>315</v>
+      </c>
+      <c r="I18" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" t="s">
+        <v>173</v>
+      </c>
+      <c r="D19" t="s">
+        <v>217</v>
+      </c>
+      <c r="E19" t="s">
+        <v>209</v>
+      </c>
+      <c r="F19" t="s">
+        <v>264</v>
+      </c>
+      <c r="G19" t="s">
+        <v>289</v>
+      </c>
+      <c r="H19" t="s">
+        <v>315</v>
+      </c>
+      <c r="I19" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>104</v>
+      </c>
+      <c r="B20" t="s">
+        <v>128</v>
+      </c>
+      <c r="C20" t="s">
+        <v>174</v>
+      </c>
+      <c r="D20" t="s">
+        <v>218</v>
+      </c>
+      <c r="E20" t="s">
+        <v>248</v>
+      </c>
+      <c r="F20" t="s">
+        <v>268</v>
+      </c>
+      <c r="G20" t="s">
+        <v>290</v>
+      </c>
+      <c r="H20" t="s">
+        <v>315</v>
+      </c>
+      <c r="I20" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>104</v>
+      </c>
+      <c r="B21" t="s">
+        <v>129</v>
+      </c>
+      <c r="C21" t="s">
+        <v>175</v>
+      </c>
+      <c r="D21" t="s">
+        <v>219</v>
+      </c>
+      <c r="E21" t="s">
+        <v>249</v>
+      </c>
+      <c r="F21" t="s">
+        <v>268</v>
+      </c>
+      <c r="G21" t="s">
+        <v>291</v>
+      </c>
+      <c r="H21" t="s">
+        <v>315</v>
+      </c>
+      <c r="I21" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>104</v>
+      </c>
+      <c r="B22" t="s">
+        <v>130</v>
+      </c>
+      <c r="C22" t="s">
+        <v>176</v>
+      </c>
+      <c r="D22" t="s">
+        <v>220</v>
+      </c>
+      <c r="E22" t="s">
+        <v>209</v>
+      </c>
+      <c r="F22" t="s">
+        <v>269</v>
+      </c>
+      <c r="G22" t="s">
+        <v>292</v>
+      </c>
+      <c r="H22" t="s">
+        <v>315</v>
+      </c>
+      <c r="I22" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>104</v>
+      </c>
+      <c r="B23" t="s">
+        <v>131</v>
+      </c>
+      <c r="C23" t="s">
+        <v>177</v>
+      </c>
+      <c r="D23" t="s">
+        <v>221</v>
+      </c>
+      <c r="E23" t="s">
+        <v>209</v>
+      </c>
+      <c r="F23" t="s">
+        <v>209</v>
+      </c>
+      <c r="G23" t="s">
+        <v>293</v>
+      </c>
+      <c r="H23" t="s">
+        <v>317</v>
+      </c>
+      <c r="I23" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>104</v>
+      </c>
+      <c r="B24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" t="s">
+        <v>178</v>
+      </c>
+      <c r="D24" t="s">
+        <v>222</v>
+      </c>
+      <c r="E24" t="s">
+        <v>249</v>
+      </c>
+      <c r="F24" t="s">
+        <v>270</v>
+      </c>
+      <c r="G24" t="s">
+        <v>294</v>
+      </c>
+      <c r="H24" t="s">
+        <v>315</v>
+      </c>
+      <c r="I24" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>104</v>
+      </c>
+      <c r="B25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C25" t="s">
+        <v>179</v>
+      </c>
+      <c r="D25" t="s">
+        <v>223</v>
+      </c>
+      <c r="E25" t="s">
+        <v>249</v>
+      </c>
+      <c r="F25" t="s">
+        <v>209</v>
+      </c>
+      <c r="G25" t="s">
+        <v>295</v>
+      </c>
+      <c r="H25" t="s">
+        <v>317</v>
+      </c>
+      <c r="I25" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>104</v>
+      </c>
+      <c r="B26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C26" t="s">
+        <v>180</v>
+      </c>
+      <c r="D26" t="s">
+        <v>224</v>
+      </c>
+      <c r="E26" t="s">
+        <v>209</v>
+      </c>
+      <c r="F26" t="s">
+        <v>209</v>
+      </c>
+      <c r="G26" t="s">
+        <v>296</v>
+      </c>
+      <c r="H26" t="s">
+        <v>315</v>
+      </c>
+      <c r="I26" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>104</v>
+      </c>
+      <c r="B27" t="s">
+        <v>135</v>
+      </c>
+      <c r="C27" t="s">
+        <v>181</v>
+      </c>
+      <c r="D27" t="s">
+        <v>225</v>
+      </c>
+      <c r="E27" t="s">
+        <v>250</v>
+      </c>
+      <c r="F27" t="s">
+        <v>209</v>
+      </c>
+      <c r="G27" t="s">
+        <v>297</v>
+      </c>
+      <c r="H27" t="s">
+        <v>317</v>
+      </c>
+      <c r="I27" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>104</v>
+      </c>
+      <c r="B28" t="s">
+        <v>136</v>
+      </c>
+      <c r="C28" t="s">
+        <v>182</v>
+      </c>
+      <c r="D28" t="s">
+        <v>226</v>
+      </c>
+      <c r="E28" t="s">
+        <v>248</v>
+      </c>
+      <c r="F28" t="s">
+        <v>209</v>
+      </c>
+      <c r="G28" t="s">
+        <v>298</v>
+      </c>
+      <c r="H28" t="s">
+        <v>317</v>
+      </c>
+      <c r="I28" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>105</v>
+      </c>
+      <c r="B29" t="s">
+        <v>137</v>
+      </c>
+      <c r="C29" t="s">
+        <v>183</v>
+      </c>
+      <c r="D29" t="s">
+        <v>227</v>
+      </c>
+      <c r="E29" t="s">
+        <v>209</v>
+      </c>
+      <c r="F29" t="s">
+        <v>264</v>
+      </c>
+      <c r="G29" t="s">
+        <v>299</v>
+      </c>
+      <c r="H29" t="s">
+        <v>315</v>
+      </c>
+      <c r="I29" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B30" t="s">
+        <v>138</v>
+      </c>
+      <c r="C30" t="s">
+        <v>184</v>
+      </c>
+      <c r="D30" t="s">
+        <v>209</v>
+      </c>
+      <c r="E30" t="s">
+        <v>209</v>
+      </c>
+      <c r="F30" t="s">
+        <v>209</v>
+      </c>
+      <c r="G30" t="s">
+        <v>298</v>
+      </c>
+      <c r="H30" t="s">
+        <v>317</v>
+      </c>
+      <c r="I30" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>105</v>
+      </c>
+      <c r="B31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C31" t="s">
+        <v>185</v>
+      </c>
+      <c r="D31" t="s">
+        <v>228</v>
+      </c>
+      <c r="E31" t="s">
+        <v>251</v>
+      </c>
+      <c r="F31" t="s">
+        <v>264</v>
+      </c>
+      <c r="G31" t="s">
+        <v>300</v>
+      </c>
+      <c r="H31" t="s">
+        <v>314</v>
+      </c>
+      <c r="I31" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B32" t="s">
+        <v>140</v>
+      </c>
+      <c r="C32" t="s">
+        <v>186</v>
+      </c>
+      <c r="D32" t="s">
+        <v>229</v>
+      </c>
+      <c r="E32" t="s">
+        <v>252</v>
+      </c>
+      <c r="F32" t="s">
+        <v>268</v>
+      </c>
+      <c r="G32" t="s">
+        <v>301</v>
+      </c>
+      <c r="H32" t="s">
+        <v>314</v>
+      </c>
+      <c r="I32" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>106</v>
+      </c>
+      <c r="B33" t="s">
+        <v>141</v>
+      </c>
+      <c r="C33" t="s">
+        <v>187</v>
+      </c>
+      <c r="D33" t="s">
+        <v>230</v>
+      </c>
+      <c r="E33" t="s">
+        <v>253</v>
+      </c>
+      <c r="F33" t="s">
+        <v>268</v>
+      </c>
+      <c r="G33" t="s">
+        <v>262</v>
+      </c>
+      <c r="H33" t="s">
+        <v>314</v>
+      </c>
+      <c r="I33" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>106</v>
+      </c>
+      <c r="B34" t="s">
+        <v>142</v>
+      </c>
+      <c r="C34" t="s">
+        <v>188</v>
+      </c>
+      <c r="D34" t="s">
+        <v>231</v>
+      </c>
+      <c r="E34" t="s">
+        <v>254</v>
+      </c>
+      <c r="F34" t="s">
+        <v>264</v>
+      </c>
+      <c r="G34" t="s">
+        <v>302</v>
+      </c>
+      <c r="H34" t="s">
+        <v>315</v>
+      </c>
+      <c r="I34" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>106</v>
+      </c>
+      <c r="B35" t="s">
+        <v>143</v>
+      </c>
+      <c r="C35" t="s">
+        <v>189</v>
+      </c>
+      <c r="D35" t="s">
+        <v>232</v>
+      </c>
+      <c r="E35" t="s">
+        <v>209</v>
+      </c>
+      <c r="F35" t="s">
+        <v>209</v>
+      </c>
+      <c r="G35" t="s">
+        <v>298</v>
+      </c>
+      <c r="H35" t="s">
+        <v>317</v>
+      </c>
+      <c r="I35" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>106</v>
+      </c>
+      <c r="B36" t="s">
+        <v>144</v>
+      </c>
+      <c r="C36" t="s">
+        <v>190</v>
+      </c>
+      <c r="D36" t="s">
+        <v>233</v>
+      </c>
+      <c r="E36" t="s">
+        <v>243</v>
+      </c>
+      <c r="F36" t="s">
+        <v>264</v>
+      </c>
+      <c r="G36" t="s">
+        <v>303</v>
+      </c>
+      <c r="H36" t="s">
+        <v>315</v>
+      </c>
+      <c r="I36" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>106</v>
+      </c>
+      <c r="B37" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" t="s">
+        <v>191</v>
+      </c>
+      <c r="D37" t="s">
+        <v>234</v>
+      </c>
+      <c r="E37" t="s">
+        <v>255</v>
+      </c>
+      <c r="F37" t="s">
+        <v>264</v>
+      </c>
+      <c r="G37" t="s">
+        <v>304</v>
+      </c>
+      <c r="H37" t="s">
+        <v>315</v>
+      </c>
+      <c r="I37" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C38" t="s">
+        <v>192</v>
+      </c>
+      <c r="D38" t="s">
+        <v>209</v>
+      </c>
+      <c r="E38" t="s">
+        <v>253</v>
+      </c>
+      <c r="F38" t="s">
+        <v>209</v>
+      </c>
+      <c r="G38" t="s">
+        <v>305</v>
+      </c>
+      <c r="H38" t="s">
+        <v>315</v>
+      </c>
+      <c r="I38" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>106</v>
+      </c>
+      <c r="B39" t="s">
+        <v>147</v>
+      </c>
+      <c r="C39" t="s">
+        <v>193</v>
+      </c>
+      <c r="D39" t="s">
+        <v>209</v>
+      </c>
+      <c r="E39" t="s">
+        <v>256</v>
+      </c>
+      <c r="F39" t="s">
+        <v>268</v>
+      </c>
+      <c r="G39" t="s">
+        <v>291</v>
+      </c>
+      <c r="H39" t="s">
+        <v>315</v>
+      </c>
+      <c r="I39" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>106</v>
+      </c>
+      <c r="B40" t="s">
+        <v>148</v>
+      </c>
+      <c r="C40" t="s">
+        <v>194</v>
+      </c>
+      <c r="D40" t="s">
+        <v>235</v>
+      </c>
+      <c r="E40" t="s">
+        <v>256</v>
+      </c>
+      <c r="F40" t="s">
+        <v>268</v>
+      </c>
+      <c r="G40" t="s">
+        <v>291</v>
+      </c>
+      <c r="H40" t="s">
+        <v>315</v>
+      </c>
+      <c r="I40" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>106</v>
+      </c>
+      <c r="B41" t="s">
+        <v>149</v>
+      </c>
+      <c r="C41" t="s">
+        <v>195</v>
+      </c>
+      <c r="D41" t="s">
+        <v>209</v>
+      </c>
+      <c r="E41" t="s">
+        <v>253</v>
+      </c>
+      <c r="F41" t="s">
+        <v>209</v>
+      </c>
+      <c r="G41" t="s">
+        <v>306</v>
+      </c>
+      <c r="H41" t="s">
+        <v>315</v>
+      </c>
+      <c r="I41" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>106</v>
+      </c>
+      <c r="B42" t="s">
+        <v>150</v>
+      </c>
+      <c r="C42" t="s">
+        <v>180</v>
+      </c>
+      <c r="D42" t="s">
+        <v>236</v>
+      </c>
+      <c r="E42" t="s">
+        <v>209</v>
+      </c>
+      <c r="F42" t="s">
+        <v>271</v>
+      </c>
+      <c r="G42" t="s">
+        <v>307</v>
+      </c>
+      <c r="H42" t="s">
+        <v>315</v>
+      </c>
+      <c r="I42" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>106</v>
+      </c>
+      <c r="B43" t="s">
+        <v>151</v>
+      </c>
+      <c r="C43" t="s">
+        <v>196</v>
+      </c>
+      <c r="D43" t="s">
+        <v>237</v>
+      </c>
+      <c r="E43" t="s">
+        <v>257</v>
+      </c>
+      <c r="F43" t="s">
+        <v>272</v>
+      </c>
+      <c r="G43" t="s">
+        <v>308</v>
+      </c>
+      <c r="H43" t="s">
+        <v>315</v>
+      </c>
+      <c r="I43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>107</v>
+      </c>
+      <c r="B44" t="s">
+        <v>152</v>
+      </c>
+      <c r="C44" t="s">
+        <v>197</v>
+      </c>
+      <c r="D44" t="s">
+        <v>238</v>
+      </c>
+      <c r="E44" t="s">
+        <v>258</v>
+      </c>
+      <c r="F44" t="s">
+        <v>209</v>
+      </c>
+      <c r="G44" t="s">
+        <v>309</v>
+      </c>
+      <c r="H44" t="s">
+        <v>317</v>
+      </c>
+      <c r="I44" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>108</v>
+      </c>
+      <c r="B45" t="s">
+        <v>153</v>
+      </c>
+      <c r="C45" t="s">
+        <v>198</v>
+      </c>
+      <c r="D45" t="s">
+        <v>209</v>
+      </c>
+      <c r="E45" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" t="s">
+        <v>209</v>
+      </c>
+      <c r="G45" t="s">
+        <v>309</v>
+      </c>
+      <c r="H45" t="s">
+        <v>317</v>
+      </c>
+      <c r="I45" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>108</v>
+      </c>
+      <c r="B46" t="s">
+        <v>154</v>
+      </c>
+      <c r="C46" t="s">
+        <v>199</v>
+      </c>
+      <c r="D46" t="s">
+        <v>209</v>
+      </c>
+      <c r="E46" t="s">
+        <v>244</v>
+      </c>
+      <c r="F46" t="s">
+        <v>209</v>
+      </c>
+      <c r="G46" t="s">
+        <v>309</v>
+      </c>
+      <c r="H46" t="s">
+        <v>317</v>
+      </c>
+      <c r="I46" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>109</v>
+      </c>
+      <c r="B47" t="s">
+        <v>155</v>
+      </c>
+      <c r="C47" t="s">
+        <v>200</v>
+      </c>
+      <c r="D47" t="s">
+        <v>239</v>
+      </c>
+      <c r="E47" t="s">
+        <v>260</v>
+      </c>
+      <c r="F47" t="s">
+        <v>209</v>
+      </c>
+      <c r="G47" t="s">
+        <v>310</v>
+      </c>
+      <c r="H47" t="s">
+        <v>319</v>
+      </c>
+      <c r="I47" t="s">
+        <v>341</v>
       </c>
     </row>
   </sheetData>
